--- a/model/Cholamandalam_Finance_Equity_Research.xlsx
+++ b/model/Cholamandalam_Finance_Equity_Research.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" r:id="R17185d51eea14e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sources" sheetId="2" r:id="R4641dba9b2244507"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Raw_Financials" sheetId="3" r:id="R639243e689d24d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Historical_Analysis" sheetId="4" r:id="R58e6e72016f44bb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Industry_Data" sheetId="5" r:id="R2448518bca4c44eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Assumptions" sheetId="6" r:id="Re7f28174118c4faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Schedules" sheetId="7" r:id="R462cd876a352411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Income_Statement" sheetId="8" r:id="Rea1578618a6041c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Balance_Sheet" sheetId="9" r:id="R8ebac3492bdf444e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Cash_Flow" sheetId="10" r:id="R5f7b69df515447f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_DCF" sheetId="11" r:id="Rac65fc70234a4d10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Reverse_DCF" sheetId="12" r:id="R31244620992b42b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" r:id="R36afa913df2341ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Sources" sheetId="2" r:id="R5d8a086dcfbf42fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Raw_Financials" sheetId="3" r:id="Rbf63476d10654289"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Historical_Analysis" sheetId="4" r:id="Rda223cd535634599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Industry_Data" sheetId="5" r:id="R0b7392e25edd4ede"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Assumptions" sheetId="6" r:id="R43a97a0680904ead"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Schedules" sheetId="7" r:id="Rb4315d59454b4323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Income_Statement" sheetId="8" r:id="R69524836669f4fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Balance_Sheet" sheetId="9" r:id="R870b96206982421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Cash_Flow" sheetId="10" r:id="Ra8c12f2640c7441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_DCF" sheetId="11" r:id="Re89f483c4d5d4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Reverse_DCF" sheetId="12" r:id="Ra7fb75034d0641fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +35,7 @@
     <x:numFmt numFmtId="207" formatCode="0.00%"/>
     <x:numFmt numFmtId="208" formatCode="0.00;(0.00);0.00"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -122,8 +122,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FF30363D"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -145,6 +151,16 @@
         <x:fgColor rgb="FF3F6F63"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -157,7 +173,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="83">
+  <x:cellXfs count="96">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -350,6 +366,45 @@
     </x:xf>
     <x:xf numFmtId="206" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -567,23 +622,23 @@
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="92" t="str">
         <x:v>Cholamandalam Finance Equity Research</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
-      <x:c r="H1" s="29"/>
-      <x:c r="I1" s="29"/>
-      <x:c r="J1" s="29"/>
-      <x:c r="K1" s="29"/>
-      <x:c r="L1" s="29"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="92"/>
+      <x:c r="C1" s="93"/>
+      <x:c r="D1" s="93"/>
+      <x:c r="E1" s="93"/>
+      <x:c r="F1" s="93"/>
+      <x:c r="G1" s="93"/>
+      <x:c r="H1" s="93"/>
+      <x:c r="I1" s="93"/>
+      <x:c r="J1" s="93"/>
+      <x:c r="K1" s="93"/>
+      <x:c r="L1" s="93"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -613,7 +668,7 @@
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -643,7 +698,7 @@
       <x:c r="K5" s="2"/>
       <x:c r="L5" s="2"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="2"/>
       <x:c r="B6" s="2"/>
       <x:c r="C6" s="2"/>
@@ -711,7 +766,7 @@
       <x:c r="K9" s="2"/>
       <x:c r="L9" s="2"/>
     </x:row>
-    <x:row r="10" ht="19" customHeight="1">
+    <x:row r="10" ht="8" customHeight="1">
       <x:c r="A10" s="2"/>
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
@@ -725,7 +780,7 @@
       <x:c r="K10" s="2"/>
       <x:c r="L10" s="2"/>
     </x:row>
-    <x:row r="11" ht="19" customHeight="1">
+    <x:row r="11" ht="8" customHeight="1">
       <x:c r="A11" s="2"/>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
@@ -755,7 +810,7 @@
       <x:c r="K12" s="2"/>
       <x:c r="L12" s="2"/>
     </x:row>
-    <x:row r="13" ht="19" customHeight="1">
+    <x:row r="13" ht="8" customHeight="1">
       <x:c r="A13" s="2"/>
       <x:c r="B13" s="2"/>
       <x:c r="C13" s="2"/>
@@ -864,7 +919,7 @@
       <x:c r="K18" s="2"/>
       <x:c r="L18" s="2"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19" s="2"/>
       <x:c r="B19" s="2"/>
       <x:c r="C19" s="2"/>
@@ -878,7 +933,7 @@
       <x:c r="K19" s="2"/>
       <x:c r="L19" s="2"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20" s="2"/>
       <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
@@ -892,7 +947,7 @@
       <x:c r="K20" s="2"/>
       <x:c r="L20" s="2"/>
     </x:row>
-    <x:row r="21" ht="19" customHeight="1">
+    <x:row r="21" ht="8" customHeight="1">
       <x:c r="A21" s="2"/>
       <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
@@ -922,7 +977,7 @@
       <x:c r="K22" s="2"/>
       <x:c r="L22" s="2"/>
     </x:row>
-    <x:row r="23" ht="19" customHeight="1">
+    <x:row r="23" ht="8" customHeight="1">
       <x:c r="A23" s="2"/>
       <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
@@ -1008,7 +1063,7 @@
       <x:c r="K27" s="2"/>
       <x:c r="L27" s="2"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="2"/>
       <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
@@ -1022,7 +1077,7 @@
       <x:c r="K28" s="2"/>
       <x:c r="L28" s="2"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29" s="2"/>
       <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
@@ -1036,10 +1091,8 @@
       <x:c r="K29" s="2"/>
       <x:c r="L29" s="2"/>
     </x:row>
-    <x:row r="30" ht="42" customHeight="1">
-      <x:c r="A30" s="12" t="str">
-        <x:v>Standalone lender forecast, three statements and equity valuation. Management guidance informs operating assumptions; valuation assumptions are identified separately.</x:v>
-      </x:c>
+    <x:row r="30" ht="8" customHeight="1">
+      <x:c r="A30" s="12"/>
       <x:c r="B30" s="12"/>
       <x:c r="C30" s="12"/>
       <x:c r="D30" s="12"/>
@@ -1052,7 +1105,7 @@
       <x:c r="K30" s="12"/>
       <x:c r="L30" s="12"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="2"/>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -1066,7 +1119,7 @@
       <x:c r="K31" s="2"/>
       <x:c r="L31" s="2"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="2"/>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -1080,7 +1133,7 @@
       <x:c r="K32" s="2"/>
       <x:c r="L32" s="2"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="2"/>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -1094,7 +1147,7 @@
       <x:c r="K33" s="2"/>
       <x:c r="L33" s="2"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34" s="2"/>
       <x:c r="B34" s="2"/>
       <x:c r="C34" s="2"/>
@@ -1108,7 +1161,7 @@
       <x:c r="K34" s="2"/>
       <x:c r="L34" s="2"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="2"/>
       <x:c r="B35" s="2"/>
       <x:c r="C35" s="2"/>
@@ -1122,7 +1175,7 @@
       <x:c r="K35" s="2"/>
       <x:c r="L35" s="2"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="2"/>
       <x:c r="B36" s="2"/>
       <x:c r="C36" s="2"/>
@@ -1136,7 +1189,7 @@
       <x:c r="K36" s="2"/>
       <x:c r="L36" s="2"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -1150,7 +1203,7 @@
       <x:c r="K37" s="2"/>
       <x:c r="L37" s="2"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="2"/>
       <x:c r="B38" s="2"/>
       <x:c r="C38" s="2"/>
@@ -1164,7 +1217,7 @@
       <x:c r="K38" s="2"/>
       <x:c r="L38" s="2"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="2"/>
       <x:c r="B39" s="2"/>
       <x:c r="C39" s="2"/>
@@ -1178,7 +1231,7 @@
       <x:c r="K39" s="2"/>
       <x:c r="L39" s="2"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="2"/>
       <x:c r="B40" s="2"/>
       <x:c r="C40" s="2"/>
@@ -1192,7 +1245,7 @@
       <x:c r="K40" s="2"/>
       <x:c r="L40" s="2"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="2"/>
       <x:c r="B41" s="2"/>
       <x:c r="C41" s="2"/>
@@ -1206,7 +1259,7 @@
       <x:c r="K41" s="2"/>
       <x:c r="L41" s="2"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="2"/>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -1220,7 +1273,7 @@
       <x:c r="K42" s="2"/>
       <x:c r="L42" s="2"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="2"/>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -1234,7 +1287,7 @@
       <x:c r="K43" s="2"/>
       <x:c r="L43" s="2"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="2"/>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -1248,7 +1301,7 @@
       <x:c r="K44" s="2"/>
       <x:c r="L44" s="2"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="2"/>
       <x:c r="B45" s="2"/>
       <x:c r="C45" s="2"/>
@@ -1262,7 +1315,7 @@
       <x:c r="K45" s="2"/>
       <x:c r="L45" s="2"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="2"/>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -1276,7 +1329,7 @@
       <x:c r="K46" s="2"/>
       <x:c r="L46" s="2"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="2"/>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -1290,7 +1343,7 @@
       <x:c r="K47" s="2"/>
       <x:c r="L47" s="2"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="2"/>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -1304,7 +1357,7 @@
       <x:c r="K48" s="2"/>
       <x:c r="L48" s="2"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="2"/>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -1318,7 +1371,7 @@
       <x:c r="K49" s="2"/>
       <x:c r="L49" s="2"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="2"/>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -1332,7 +1385,7 @@
       <x:c r="K50" s="2"/>
       <x:c r="L50" s="2"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="2"/>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -1346,7 +1399,7 @@
       <x:c r="K51" s="2"/>
       <x:c r="L51" s="2"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="2"/>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -1360,7 +1413,7 @@
       <x:c r="K52" s="2"/>
       <x:c r="L52" s="2"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="2"/>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -1374,7 +1427,7 @@
       <x:c r="K53" s="2"/>
       <x:c r="L53" s="2"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="2"/>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -1388,7 +1441,7 @@
       <x:c r="K54" s="2"/>
       <x:c r="L54" s="2"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="2"/>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -1402,7 +1455,7 @@
       <x:c r="K55" s="2"/>
       <x:c r="L55" s="2"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="2"/>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -1416,7 +1469,7 @@
       <x:c r="K56" s="2"/>
       <x:c r="L56" s="2"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="2"/>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -1430,7 +1483,7 @@
       <x:c r="K57" s="2"/>
       <x:c r="L57" s="2"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="2"/>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -1444,7 +1497,7 @@
       <x:c r="K58" s="2"/>
       <x:c r="L58" s="2"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="2"/>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -1458,7 +1511,7 @@
       <x:c r="K59" s="2"/>
       <x:c r="L59" s="2"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="2"/>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -1472,7 +1525,7 @@
       <x:c r="K60" s="2"/>
       <x:c r="L60" s="2"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="2"/>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -1486,7 +1539,7 @@
       <x:c r="K61" s="2"/>
       <x:c r="L61" s="2"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="2"/>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -1500,7 +1553,7 @@
       <x:c r="K62" s="2"/>
       <x:c r="L62" s="2"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="2"/>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -1514,7 +1567,7 @@
       <x:c r="K63" s="2"/>
       <x:c r="L63" s="2"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="2"/>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -1528,7 +1581,7 @@
       <x:c r="K64" s="2"/>
       <x:c r="L64" s="2"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="2"/>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -2593,9 +2646,6 @@
       <x:c r="L140" s="2"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A30:G30"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2618,23 +2668,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Cash Flow Statement</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -2664,7 +2714,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -2714,7 +2764,7 @@
         <x:v>FY2031E</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -3066,7 +3116,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="19" customHeight="1">
+    <x:row r="15" ht="8" customHeight="1">
       <x:c r="A15" s="21"/>
       <x:c r="B15" s="21"/>
       <x:c r="C15" s="21"/>
@@ -3080,7 +3130,7 @@
       <x:c r="K15" s="21"/>
       <x:c r="L15" s="21"/>
     </x:row>
-    <x:row r="16" ht="19" customHeight="1">
+    <x:row r="16" ht="8" customHeight="1">
       <x:c r="A16" s="21"/>
       <x:c r="B16" s="21"/>
       <x:c r="C16" s="21"/>
@@ -3094,7 +3144,7 @@
       <x:c r="K16" s="21"/>
       <x:c r="L16" s="21"/>
     </x:row>
-    <x:row r="17" ht="30" customHeight="1">
+    <x:row r="17" ht="8" customHeight="1">
       <x:c r="A17"/>
       <x:c r="B17"/>
       <x:c r="C17"/>
@@ -3124,7 +3174,7 @@
       <x:c r="K18" s="55"/>
       <x:c r="L18" s="55"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19"/>
       <x:c r="B19"/>
       <x:c r="C19"/>
@@ -3324,7 +3374,7 @@
         <x:v>-59423.31177682899</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26"/>
       <x:c r="B26"/>
       <x:c r="C26" s="68"/>
@@ -3431,7 +3481,7 @@
         <x:v>-2815.5682352394024</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30"/>
       <x:c r="B30"/>
       <x:c r="C30" s="68"/>
@@ -3600,7 +3650,7 @@
         <x:v>64927.04154489391</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36"/>
       <x:c r="B36"/>
       <x:c r="C36"/>
@@ -3614,7 +3664,7 @@
       <x:c r="K36"/>
       <x:c r="L36"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37"/>
       <x:c r="B37"/>
       <x:c r="C37"/>
@@ -3628,37 +3678,39 @@
       <x:c r="K37"/>
       <x:c r="L37"/>
     </x:row>
-    <x:row r="38" ht="42" customHeight="1">
-      <x:c r="A38" s="52" t="str">
-        <x:v>Forecast cash flows use net loan and balance-sheet changes, maintenance investment equal to D&amp;A, and aggregate funding. No impairment add-back is made against net loans. CCD conversion is noncash.</x:v>
-      </x:c>
-      <x:c r="B38" s="52"/>
-      <x:c r="C38" s="52"/>
-      <x:c r="D38" s="52"/>
-      <x:c r="E38" s="52"/>
-      <x:c r="F38" s="52"/>
-      <x:c r="G38" s="52"/>
-      <x:c r="H38" s="52"/>
-      <x:c r="I38" s="52"/>
-      <x:c r="J38" s="52"/>
-      <x:c r="K38" s="52"/>
-      <x:c r="L38" s="52"/>
+    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A38" s="91" t="str">
+        <x:v>Simplified cash flow uses changes in net loans. Maintenance capital expenditure equals depreciation.</x:v>
+      </x:c>
+      <x:c r="B38" s="91"/>
+      <x:c r="C38" s="91"/>
+      <x:c r="D38" s="91"/>
+      <x:c r="E38" s="91"/>
+      <x:c r="F38" s="91"/>
+      <x:c r="G38" s="91"/>
+      <x:c r="H38" s="91"/>
+      <x:c r="I38" s="91"/>
+      <x:c r="J38" s="91"/>
+      <x:c r="K38" s="91"/>
+      <x:c r="L38" s="91"/>
     </x:row>
     <x:row r="39" ht="19" customHeight="1">
-      <x:c r="A39"/>
-      <x:c r="B39"/>
-      <x:c r="C39"/>
-      <x:c r="D39"/>
-      <x:c r="E39"/>
-      <x:c r="F39"/>
-      <x:c r="G39"/>
-      <x:c r="H39"/>
-      <x:c r="I39"/>
-      <x:c r="J39"/>
-      <x:c r="K39"/>
-      <x:c r="L39"/>
-    </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+      <x:c r="A39" s="91" t="str">
+        <x:v>Funding is aggregated. Impairment is not added back against net loans. CCD conversion is non-cash.</x:v>
+      </x:c>
+      <x:c r="B39" s="91"/>
+      <x:c r="C39" s="91"/>
+      <x:c r="D39" s="91"/>
+      <x:c r="E39" s="91"/>
+      <x:c r="F39" s="91"/>
+      <x:c r="G39" s="91"/>
+      <x:c r="H39" s="91"/>
+      <x:c r="I39" s="91"/>
+      <x:c r="J39" s="91"/>
+      <x:c r="K39" s="91"/>
+      <x:c r="L39" s="91"/>
+    </x:row>
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40"/>
       <x:c r="B40"/>
       <x:c r="C40"/>
@@ -3672,7 +3724,7 @@
       <x:c r="K40"/>
       <x:c r="L40"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -3686,7 +3738,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -3700,7 +3752,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -3714,7 +3766,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -3728,7 +3780,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -3742,7 +3794,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -3756,7 +3808,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -3770,7 +3822,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -3784,7 +3836,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -3798,7 +3850,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -3812,7 +3864,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -3826,7 +3878,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -3840,7 +3892,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -3854,7 +3906,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -3868,7 +3920,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -3882,7 +3934,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -3896,7 +3948,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -3910,7 +3962,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -3924,7 +3976,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -3938,7 +3990,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -3952,7 +4004,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -3966,7 +4018,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -3980,7 +4032,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -3994,7 +4046,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -4008,7 +4060,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -5073,9 +5125,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A38:L38"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -5098,23 +5147,23 @@
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>FCFE Valuation</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -5144,7 +5193,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -5174,7 +5223,7 @@
       <x:c r="K5" s="21"/>
       <x:c r="L5" s="21"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -5283,7 +5332,7 @@
       <x:c r="K11" s="21"/>
       <x:c r="L11" s="21"/>
     </x:row>
-    <x:row r="12" ht="19" customHeight="1">
+    <x:row r="12" ht="8" customHeight="1">
       <x:c r="A12" s="21"/>
       <x:c r="B12" s="21"/>
       <x:c r="C12" s="21"/>
@@ -5297,7 +5346,7 @@
       <x:c r="K12" s="21"/>
       <x:c r="L12" s="21"/>
     </x:row>
-    <x:row r="13" ht="19" customHeight="1">
+    <x:row r="13" ht="8" customHeight="1">
       <x:c r="A13" s="21"/>
       <x:c r="B13" s="21"/>
       <x:c r="C13" s="21"/>
@@ -5717,7 +5766,7 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30" s="21"/>
       <x:c r="B30" s="21"/>
       <x:c r="C30" s="21"/>
@@ -5731,7 +5780,7 @@
       <x:c r="K30" s="21"/>
       <x:c r="L30" s="21"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="21"/>
       <x:c r="C31" s="21"/>
@@ -5745,23 +5794,23 @@
       <x:c r="K31" s="21"/>
       <x:c r="L31" s="21"/>
     </x:row>
-    <x:row r="32" ht="42" customHeight="1">
-      <x:c r="A32" s="36" t="str">
-        <x:v>FCFE = PAT less the increase in required book equity. The 14% equity/net-loan assumption measures reinvestment; regulatory CAR includes Tier 2 and is not substituted for common equity.</x:v>
-      </x:c>
-      <x:c r="B32" s="36"/>
-      <x:c r="C32" s="36"/>
-      <x:c r="D32" s="36"/>
-      <x:c r="E32" s="36"/>
-      <x:c r="F32" s="36"/>
-      <x:c r="G32" s="36"/>
-      <x:c r="H32" s="36"/>
-      <x:c r="I32" s="36"/>
-      <x:c r="J32" s="36"/>
-      <x:c r="K32" s="36"/>
-      <x:c r="L32" s="36"/>
-    </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" s="91" t="str">
+        <x:v>FCFE = profit after tax less the increase in required book equity (14% of net loans, not regulatory CAR).</x:v>
+      </x:c>
+      <x:c r="B32" s="91"/>
+      <x:c r="C32" s="91"/>
+      <x:c r="D32" s="91"/>
+      <x:c r="E32" s="91"/>
+      <x:c r="F32" s="91"/>
+      <x:c r="G32" s="91"/>
+      <x:c r="H32" s="91"/>
+      <x:c r="I32" s="91"/>
+      <x:c r="J32" s="91"/>
+      <x:c r="K32" s="91"/>
+      <x:c r="L32" s="91"/>
+    </x:row>
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="21"/>
       <x:c r="B33" s="21"/>
       <x:c r="C33" s="21"/>
@@ -5775,23 +5824,23 @@
       <x:c r="K33" s="21"/>
       <x:c r="L33" s="21"/>
     </x:row>
-    <x:row r="34" ht="42" customHeight="1">
-      <x:c r="A34" s="36" t="str">
-        <x:v>Value date: 18-Sep-2026. FY2027 FCFE is prorated for the remaining year and discounted over that fraction; later years use year-end timing. This is an annual-model timing approximation.</x:v>
-      </x:c>
-      <x:c r="B34" s="36"/>
-      <x:c r="C34" s="36"/>
-      <x:c r="D34" s="36"/>
-      <x:c r="E34" s="36"/>
-      <x:c r="F34" s="36"/>
-      <x:c r="G34" s="36"/>
-      <x:c r="H34" s="36"/>
-      <x:c r="I34" s="36"/>
-      <x:c r="J34" s="36"/>
-      <x:c r="K34" s="36"/>
-      <x:c r="L34" s="36"/>
-    </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" s="91" t="str">
+        <x:v>Valuation date: 18 September 2026. FY2027 FCFE is prorated for the remaining year. Later flows are year-end.</x:v>
+      </x:c>
+      <x:c r="B34" s="91"/>
+      <x:c r="C34" s="91"/>
+      <x:c r="D34" s="91"/>
+      <x:c r="E34" s="91"/>
+      <x:c r="F34" s="91"/>
+      <x:c r="G34" s="91"/>
+      <x:c r="H34" s="91"/>
+      <x:c r="I34" s="91"/>
+      <x:c r="J34" s="91"/>
+      <x:c r="K34" s="91"/>
+      <x:c r="L34" s="91"/>
+    </x:row>
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="21"/>
       <x:c r="B35" s="21"/>
       <x:c r="C35" s="21"/>
@@ -5805,37 +5854,39 @@
       <x:c r="K35" s="21"/>
       <x:c r="L35" s="21"/>
     </x:row>
-    <x:row r="36" ht="42" customHeight="1">
-      <x:c r="A36" s="36" t="str">
-        <x:v>Terminal PAT = FY2031 required equity x terminal ROE. Terminal equity investment = FY2031 required equity x terminal growth. Pro forma shares include estimated CCD dilution; no excess capital is added.</x:v>
-      </x:c>
-      <x:c r="B36" s="36"/>
-      <x:c r="C36" s="36"/>
-      <x:c r="D36" s="36"/>
-      <x:c r="E36" s="36"/>
-      <x:c r="F36" s="36"/>
-      <x:c r="G36" s="36"/>
-      <x:c r="H36" s="21"/>
-      <x:c r="I36" s="21"/>
-      <x:c r="J36" s="21"/>
-      <x:c r="K36" s="21"/>
-      <x:c r="L36" s="21"/>
+    <x:row r="36" ht="19" customHeight="1">
+      <x:c r="A36" s="91" t="str">
+        <x:v>Terminal profit = FY2031 required equity × terminal ROE. Reinvestment = required equity × terminal growth.</x:v>
+      </x:c>
+      <x:c r="B36" s="91"/>
+      <x:c r="C36" s="91"/>
+      <x:c r="D36" s="91"/>
+      <x:c r="E36" s="91"/>
+      <x:c r="F36" s="91"/>
+      <x:c r="G36" s="91"/>
+      <x:c r="H36" s="91"/>
+      <x:c r="I36" s="91"/>
+      <x:c r="J36" s="91"/>
+      <x:c r="K36" s="91"/>
+      <x:c r="L36" s="91"/>
     </x:row>
     <x:row r="37" ht="19" customHeight="1">
-      <x:c r="A37" s="21"/>
-      <x:c r="B37" s="21"/>
-      <x:c r="C37" s="21"/>
-      <x:c r="D37" s="21"/>
-      <x:c r="E37" s="21"/>
-      <x:c r="F37" s="21"/>
-      <x:c r="G37" s="21"/>
-      <x:c r="H37" s="21"/>
-      <x:c r="I37" s="21"/>
-      <x:c r="J37" s="21"/>
-      <x:c r="K37" s="21"/>
-      <x:c r="L37" s="21"/>
-    </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A37" s="91" t="str">
+        <x:v>Pro-forma shares include CCD conversion. No additional excess-capital distribution is assumed.</x:v>
+      </x:c>
+      <x:c r="B37" s="91"/>
+      <x:c r="C37" s="91"/>
+      <x:c r="D37" s="91"/>
+      <x:c r="E37" s="91"/>
+      <x:c r="F37" s="91"/>
+      <x:c r="G37" s="91"/>
+      <x:c r="H37" s="91"/>
+      <x:c r="I37" s="91"/>
+      <x:c r="J37" s="91"/>
+      <x:c r="K37" s="91"/>
+      <x:c r="L37" s="91"/>
+    </x:row>
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="21"/>
       <x:c r="C38" s="21"/>
@@ -5849,7 +5900,7 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="21"/>
       <x:c r="C39" s="21"/>
@@ -5863,7 +5914,7 @@
       <x:c r="K39" s="21"/>
       <x:c r="L39" s="21"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -5877,7 +5928,7 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -5891,7 +5942,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -5905,7 +5956,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -5919,7 +5970,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -5933,7 +5984,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -5947,7 +5998,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -5961,7 +6012,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -5975,7 +6026,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -5989,7 +6040,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -6003,7 +6054,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -6017,7 +6068,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -6031,7 +6082,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -6045,7 +6096,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -6059,7 +6110,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -6073,7 +6124,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -6087,7 +6138,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -6101,7 +6152,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -6115,7 +6166,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -6129,7 +6180,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -6143,7 +6194,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -6157,7 +6208,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -6171,7 +6222,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -6185,7 +6236,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -6199,7 +6250,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -6213,7 +6264,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -7278,11 +7329,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A32:G32"/>
-    <x:mergeCell ref="A34:G34"/>
-    <x:mergeCell ref="A36:G36"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -7305,23 +7351,23 @@
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Reverse DCF</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -7351,7 +7397,7 @@
       <x:c r="K3"/>
       <x:c r="L3"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4"/>
       <x:c r="B4"/>
       <x:c r="C4"/>
@@ -7381,7 +7427,7 @@
       <x:c r="K5" s="55"/>
       <x:c r="L5" s="55"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
@@ -7547,7 +7593,7 @@
       <x:c r="K14"/>
       <x:c r="L14"/>
     </x:row>
-    <x:row r="15" ht="19" customHeight="1">
+    <x:row r="15" ht="8" customHeight="1">
       <x:c r="A15"/>
       <x:c r="B15"/>
       <x:c r="C15" s="68"/>
@@ -7618,7 +7664,7 @@
       <x:c r="K18"/>
       <x:c r="L18"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19"/>
       <x:c r="B19"/>
       <x:c r="C19"/>
@@ -7632,7 +7678,7 @@
       <x:c r="K19"/>
       <x:c r="L19"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20"/>
       <x:c r="B20"/>
       <x:c r="C20"/>
@@ -7646,23 +7692,23 @@
       <x:c r="K20"/>
       <x:c r="L20"/>
     </x:row>
-    <x:row r="21" ht="42" customHeight="1">
-      <x:c r="A21" s="52" t="str">
-        <x:v>The reverse DCF solves the terminal ROE needed to match the reference price while holding the five-year forecast, capital intensity, discount rate and terminal growth constant. It is a market expectation, not a forecast.</x:v>
-      </x:c>
-      <x:c r="B21" s="52"/>
-      <x:c r="C21" s="52"/>
-      <x:c r="D21" s="52"/>
-      <x:c r="E21" s="52"/>
-      <x:c r="F21" s="52"/>
-      <x:c r="G21" s="52"/>
-      <x:c r="H21"/>
-      <x:c r="I21"/>
-      <x:c r="J21"/>
-      <x:c r="K21"/>
-      <x:c r="L21"/>
-    </x:row>
-    <x:row r="22" ht="19" customHeight="1">
+    <x:row r="21" ht="19" customHeight="1">
+      <x:c r="A21" s="91" t="str">
+        <x:v>Reverse DCF solves terminal ROE at the reference share price. Forecasts, capital, cost of equity and growth stay fixed.</x:v>
+      </x:c>
+      <x:c r="B21" s="91"/>
+      <x:c r="C21" s="91"/>
+      <x:c r="D21" s="91"/>
+      <x:c r="E21" s="91"/>
+      <x:c r="F21" s="91"/>
+      <x:c r="G21" s="91"/>
+      <x:c r="H21" s="91"/>
+      <x:c r="I21" s="91"/>
+      <x:c r="J21" s="91"/>
+      <x:c r="K21" s="91"/>
+      <x:c r="L21" s="91"/>
+    </x:row>
+    <x:row r="22" ht="8" customHeight="1">
       <x:c r="A22"/>
       <x:c r="B22"/>
       <x:c r="C22"/>
@@ -7676,10 +7722,8 @@
       <x:c r="K22"/>
       <x:c r="L22"/>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="52" t="str">
-        <x:v>Implied terminal ROE is conditional on the selected discount rate, terminal growth and forecast equity capital. The repriced value matches the reference share price.</x:v>
-      </x:c>
+    <x:row r="23" ht="8" customHeight="1">
+      <x:c r="A23" s="52"/>
       <x:c r="B23" s="52"/>
       <x:c r="C23" s="52"/>
       <x:c r="D23" s="52"/>
@@ -7692,7 +7736,7 @@
       <x:c r="K23"/>
       <x:c r="L23"/>
     </x:row>
-    <x:row r="24" ht="19" customHeight="1">
+    <x:row r="24" ht="8" customHeight="1">
       <x:c r="A24"/>
       <x:c r="B24"/>
       <x:c r="C24"/>
@@ -7706,7 +7750,7 @@
       <x:c r="K24"/>
       <x:c r="L24"/>
     </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25"/>
       <x:c r="B25"/>
       <x:c r="C25"/>
@@ -7720,7 +7764,7 @@
       <x:c r="K25"/>
       <x:c r="L25"/>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26"/>
       <x:c r="B26"/>
       <x:c r="C26"/>
@@ -7734,7 +7778,7 @@
       <x:c r="K26"/>
       <x:c r="L26"/>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27"/>
       <x:c r="B27"/>
       <x:c r="C27"/>
@@ -7748,7 +7792,7 @@
       <x:c r="K27"/>
       <x:c r="L27"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28"/>
       <x:c r="B28"/>
       <x:c r="C28"/>
@@ -7762,7 +7806,7 @@
       <x:c r="K28"/>
       <x:c r="L28"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29"/>
       <x:c r="B29"/>
       <x:c r="C29"/>
@@ -7776,7 +7820,7 @@
       <x:c r="K29"/>
       <x:c r="L29"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30"/>
       <x:c r="B30"/>
       <x:c r="C30"/>
@@ -7790,7 +7834,7 @@
       <x:c r="K30"/>
       <x:c r="L30"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31"/>
       <x:c r="B31"/>
       <x:c r="C31"/>
@@ -7804,7 +7848,7 @@
       <x:c r="K31"/>
       <x:c r="L31"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32"/>
       <x:c r="B32"/>
       <x:c r="C32"/>
@@ -7818,7 +7862,7 @@
       <x:c r="K32"/>
       <x:c r="L32"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33"/>
       <x:c r="B33"/>
       <x:c r="C33"/>
@@ -7832,7 +7876,7 @@
       <x:c r="K33"/>
       <x:c r="L33"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34"/>
       <x:c r="B34"/>
       <x:c r="C34"/>
@@ -7846,7 +7890,7 @@
       <x:c r="K34"/>
       <x:c r="L34"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35"/>
       <x:c r="B35"/>
       <x:c r="C35"/>
@@ -7860,7 +7904,7 @@
       <x:c r="K35"/>
       <x:c r="L35"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="21"/>
       <x:c r="B36" s="21"/>
       <x:c r="C36" s="21"/>
@@ -7874,7 +7918,7 @@
       <x:c r="K36" s="21"/>
       <x:c r="L36" s="21"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="21"/>
       <x:c r="B37" s="21"/>
       <x:c r="C37" s="21"/>
@@ -7888,7 +7932,7 @@
       <x:c r="K37" s="21"/>
       <x:c r="L37" s="21"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="21"/>
       <x:c r="C38" s="21"/>
@@ -7902,7 +7946,7 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="21"/>
       <x:c r="C39" s="21"/>
@@ -7916,7 +7960,7 @@
       <x:c r="K39" s="21"/>
       <x:c r="L39" s="21"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -7930,7 +7974,7 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -7944,7 +7988,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -7958,7 +8002,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -7972,7 +8016,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -7986,7 +8030,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -8000,7 +8044,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -8014,7 +8058,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -8028,7 +8072,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -8042,7 +8086,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -8056,7 +8100,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -8070,7 +8114,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -8084,7 +8128,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -8098,7 +8142,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -8112,7 +8156,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -8126,7 +8170,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -8140,7 +8184,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -8154,7 +8198,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -8168,7 +8212,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -8182,7 +8226,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -8196,7 +8240,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -8210,7 +8254,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -8224,7 +8268,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -8238,7 +8282,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -8252,7 +8296,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -8266,7 +8310,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -9331,10 +9375,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A21:G21"/>
-    <x:mergeCell ref="A23:G23"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -9357,23 +9397,23 @@
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="92" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
-      <x:c r="H1" s="29"/>
-      <x:c r="I1" s="29"/>
-      <x:c r="J1" s="29"/>
-      <x:c r="K1" s="29"/>
-      <x:c r="L1" s="29"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="92"/>
+      <x:c r="C1" s="93"/>
+      <x:c r="D1" s="93"/>
+      <x:c r="E1" s="93"/>
+      <x:c r="F1" s="93"/>
+      <x:c r="G1" s="93"/>
+      <x:c r="H1" s="93"/>
+      <x:c r="I1" s="93"/>
+      <x:c r="J1" s="93"/>
+      <x:c r="K1" s="93"/>
+      <x:c r="L1" s="93"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -9403,7 +9443,7 @@
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -9637,7 +9677,7 @@
       <x:c r="K14"/>
       <x:c r="L14"/>
     </x:row>
-    <x:row r="15" ht="19" customHeight="1">
+    <x:row r="15" ht="8" customHeight="1">
       <x:c r="A15"/>
       <x:c r="B15"/>
       <x:c r="C15"/>
@@ -9651,7 +9691,7 @@
       <x:c r="K15"/>
       <x:c r="L15"/>
     </x:row>
-    <x:row r="16" ht="19" customHeight="1">
+    <x:row r="16" ht="8" customHeight="1">
       <x:c r="A16"/>
       <x:c r="B16"/>
       <x:c r="C16"/>
@@ -9665,7 +9705,7 @@
       <x:c r="K16"/>
       <x:c r="L16"/>
     </x:row>
-    <x:row r="17" ht="19" customHeight="1">
+    <x:row r="17" ht="8" customHeight="1">
       <x:c r="A17"/>
       <x:c r="B17"/>
       <x:c r="C17"/>
@@ -9679,7 +9719,7 @@
       <x:c r="K17"/>
       <x:c r="L17"/>
     </x:row>
-    <x:row r="18" ht="19" customHeight="1">
+    <x:row r="18" ht="8" customHeight="1">
       <x:c r="A18"/>
       <x:c r="B18"/>
       <x:c r="C18"/>
@@ -9693,7 +9733,7 @@
       <x:c r="K18"/>
       <x:c r="L18"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19"/>
       <x:c r="B19"/>
       <x:c r="C19"/>
@@ -9707,7 +9747,7 @@
       <x:c r="K19"/>
       <x:c r="L19"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20"/>
       <x:c r="B20"/>
       <x:c r="C20"/>
@@ -9721,7 +9761,7 @@
       <x:c r="K20"/>
       <x:c r="L20"/>
     </x:row>
-    <x:row r="21" ht="19" customHeight="1">
+    <x:row r="21" ht="8" customHeight="1">
       <x:c r="A21"/>
       <x:c r="B21"/>
       <x:c r="C21"/>
@@ -9735,7 +9775,7 @@
       <x:c r="K21"/>
       <x:c r="L21"/>
     </x:row>
-    <x:row r="22" ht="19" customHeight="1">
+    <x:row r="22" ht="8" customHeight="1">
       <x:c r="A22"/>
       <x:c r="B22"/>
       <x:c r="C22"/>
@@ -9749,7 +9789,7 @@
       <x:c r="K22"/>
       <x:c r="L22"/>
     </x:row>
-    <x:row r="23" ht="19" customHeight="1">
+    <x:row r="23" ht="8" customHeight="1">
       <x:c r="A23"/>
       <x:c r="B23"/>
       <x:c r="C23"/>
@@ -9763,7 +9803,7 @@
       <x:c r="K23"/>
       <x:c r="L23"/>
     </x:row>
-    <x:row r="24" ht="19" customHeight="1">
+    <x:row r="24" ht="8" customHeight="1">
       <x:c r="A24"/>
       <x:c r="B24"/>
       <x:c r="C24"/>
@@ -9777,7 +9817,7 @@
       <x:c r="K24"/>
       <x:c r="L24"/>
     </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25"/>
       <x:c r="B25"/>
       <x:c r="C25"/>
@@ -9791,7 +9831,7 @@
       <x:c r="K25"/>
       <x:c r="L25"/>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26" s="2"/>
       <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
@@ -9805,7 +9845,7 @@
       <x:c r="K26" s="2"/>
       <x:c r="L26" s="2"/>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27" s="2"/>
       <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
@@ -9819,7 +9859,7 @@
       <x:c r="K27" s="2"/>
       <x:c r="L27" s="2"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="2"/>
       <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
@@ -9833,7 +9873,7 @@
       <x:c r="K28" s="2"/>
       <x:c r="L28" s="2"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29" s="2"/>
       <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
@@ -9847,7 +9887,7 @@
       <x:c r="K29" s="2"/>
       <x:c r="L29" s="2"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30" s="2"/>
       <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
@@ -9861,7 +9901,7 @@
       <x:c r="K30" s="2"/>
       <x:c r="L30" s="2"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="2"/>
       <x:c r="B31" s="2"/>
       <x:c r="C31" s="2"/>
@@ -9875,7 +9915,7 @@
       <x:c r="K31" s="2"/>
       <x:c r="L31" s="2"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="2"/>
       <x:c r="B32" s="2"/>
       <x:c r="C32" s="2"/>
@@ -9889,7 +9929,7 @@
       <x:c r="K32" s="2"/>
       <x:c r="L32" s="2"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="2"/>
       <x:c r="B33" s="2"/>
       <x:c r="C33" s="2"/>
@@ -9903,7 +9943,7 @@
       <x:c r="K33" s="2"/>
       <x:c r="L33" s="2"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34" s="2"/>
       <x:c r="B34" s="2"/>
       <x:c r="C34" s="2"/>
@@ -9917,7 +9957,7 @@
       <x:c r="K34" s="2"/>
       <x:c r="L34" s="2"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="2"/>
       <x:c r="B35" s="2"/>
       <x:c r="C35" s="2"/>
@@ -9931,7 +9971,7 @@
       <x:c r="K35" s="2"/>
       <x:c r="L35" s="2"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="2"/>
       <x:c r="B36" s="2"/>
       <x:c r="C36" s="2"/>
@@ -9945,7 +9985,7 @@
       <x:c r="K36" s="2"/>
       <x:c r="L36" s="2"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -9959,7 +9999,7 @@
       <x:c r="K37" s="2"/>
       <x:c r="L37" s="2"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="2"/>
       <x:c r="B38" s="2"/>
       <x:c r="C38" s="2"/>
@@ -9973,7 +10013,7 @@
       <x:c r="K38" s="2"/>
       <x:c r="L38" s="2"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="2"/>
       <x:c r="B39" s="2"/>
       <x:c r="C39" s="2"/>
@@ -9987,7 +10027,7 @@
       <x:c r="K39" s="2"/>
       <x:c r="L39" s="2"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="2"/>
       <x:c r="B40" s="2"/>
       <x:c r="C40" s="2"/>
@@ -10001,7 +10041,7 @@
       <x:c r="K40" s="2"/>
       <x:c r="L40" s="2"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="2"/>
       <x:c r="B41" s="2"/>
       <x:c r="C41" s="2"/>
@@ -10015,7 +10055,7 @@
       <x:c r="K41" s="2"/>
       <x:c r="L41" s="2"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="2"/>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -10029,7 +10069,7 @@
       <x:c r="K42" s="2"/>
       <x:c r="L42" s="2"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="2"/>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -10043,7 +10083,7 @@
       <x:c r="K43" s="2"/>
       <x:c r="L43" s="2"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="2"/>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -10057,7 +10097,7 @@
       <x:c r="K44" s="2"/>
       <x:c r="L44" s="2"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="2"/>
       <x:c r="B45" s="2"/>
       <x:c r="C45" s="2"/>
@@ -10071,7 +10111,7 @@
       <x:c r="K45" s="2"/>
       <x:c r="L45" s="2"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="2"/>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -10085,7 +10125,7 @@
       <x:c r="K46" s="2"/>
       <x:c r="L46" s="2"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="2"/>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -10099,7 +10139,7 @@
       <x:c r="K47" s="2"/>
       <x:c r="L47" s="2"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="2"/>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -10113,7 +10153,7 @@
       <x:c r="K48" s="2"/>
       <x:c r="L48" s="2"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="2"/>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -10127,7 +10167,7 @@
       <x:c r="K49" s="2"/>
       <x:c r="L49" s="2"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="2"/>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -10141,7 +10181,7 @@
       <x:c r="K50" s="2"/>
       <x:c r="L50" s="2"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="2"/>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -10155,7 +10195,7 @@
       <x:c r="K51" s="2"/>
       <x:c r="L51" s="2"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="2"/>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -10169,7 +10209,7 @@
       <x:c r="K52" s="2"/>
       <x:c r="L52" s="2"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="2"/>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -10183,7 +10223,7 @@
       <x:c r="K53" s="2"/>
       <x:c r="L53" s="2"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="2"/>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -10197,7 +10237,7 @@
       <x:c r="K54" s="2"/>
       <x:c r="L54" s="2"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="2"/>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -10211,7 +10251,7 @@
       <x:c r="K55" s="2"/>
       <x:c r="L55" s="2"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="2"/>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -10225,7 +10265,7 @@
       <x:c r="K56" s="2"/>
       <x:c r="L56" s="2"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="2"/>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -10239,7 +10279,7 @@
       <x:c r="K57" s="2"/>
       <x:c r="L57" s="2"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="2"/>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -10253,7 +10293,7 @@
       <x:c r="K58" s="2"/>
       <x:c r="L58" s="2"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="2"/>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -10267,7 +10307,7 @@
       <x:c r="K59" s="2"/>
       <x:c r="L59" s="2"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="2"/>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -10281,7 +10321,7 @@
       <x:c r="K60" s="2"/>
       <x:c r="L60" s="2"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="2"/>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -10295,7 +10335,7 @@
       <x:c r="K61" s="2"/>
       <x:c r="L61" s="2"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="2"/>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -10309,7 +10349,7 @@
       <x:c r="K62" s="2"/>
       <x:c r="L62" s="2"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="2"/>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -10323,7 +10363,7 @@
       <x:c r="K63" s="2"/>
       <x:c r="L63" s="2"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="2"/>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -10337,7 +10377,7 @@
       <x:c r="K64" s="2"/>
       <x:c r="L64" s="2"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="2"/>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -11424,23 +11464,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Historical Financial Statements</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -11470,7 +11510,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -11510,7 +11550,7 @@
       <x:c r="K5" s="32"/>
       <x:c r="L5" s="32"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -11826,7 +11866,7 @@
       <x:c r="K18" s="21"/>
       <x:c r="L18" s="21"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19" s="21"/>
       <x:c r="B19" s="21"/>
       <x:c r="C19" s="38"/>
@@ -11840,7 +11880,7 @@
       <x:c r="K19" s="21"/>
       <x:c r="L19" s="21"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20" s="21"/>
       <x:c r="B20" s="21"/>
       <x:c r="C20" s="38"/>
@@ -12104,7 +12144,7 @@
       <x:c r="K30" s="21"/>
       <x:c r="L30" s="21"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="21"/>
       <x:c r="C31" s="38"/>
@@ -12118,7 +12158,7 @@
       <x:c r="K31" s="21"/>
       <x:c r="L31" s="21"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="21"/>
       <x:c r="B32" s="21"/>
       <x:c r="C32" s="38"/>
@@ -12486,7 +12526,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="38"/>
@@ -12500,7 +12540,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="38"/>
@@ -12514,7 +12554,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="30" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="36"/>
       <x:c r="B49" s="36"/>
       <x:c r="C49" s="42"/>
@@ -12738,7 +12778,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -12752,37 +12792,39 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="42" customHeight="1">
-      <x:c r="A61" s="36" t="str">
-        <x:v>Standalone audited statements. Reported NIM includes fees and other income after funding costs. Historical regulatory ratios are disclosed figures; AUM is distinct from net loans.</x:v>
-      </x:c>
-      <x:c r="B61" s="36"/>
-      <x:c r="C61" s="36"/>
-      <x:c r="D61" s="36"/>
-      <x:c r="E61" s="36"/>
-      <x:c r="F61" s="36"/>
-      <x:c r="G61" s="36"/>
-      <x:c r="H61" s="36"/>
-      <x:c r="I61" s="36"/>
-      <x:c r="J61" s="36"/>
-      <x:c r="K61" s="36"/>
-      <x:c r="L61" s="36"/>
+    <x:row r="61" ht="19" customHeight="1">
+      <x:c r="A61" s="91" t="str">
+        <x:v>Standalone audited statements. AUM and net loans are different measures.</x:v>
+      </x:c>
+      <x:c r="B61" s="91"/>
+      <x:c r="C61" s="91"/>
+      <x:c r="D61" s="91"/>
+      <x:c r="E61" s="91"/>
+      <x:c r="F61" s="91"/>
+      <x:c r="G61" s="91"/>
+      <x:c r="H61" s="91"/>
+      <x:c r="I61" s="91"/>
+      <x:c r="J61" s="91"/>
+      <x:c r="K61" s="91"/>
+      <x:c r="L61" s="91"/>
     </x:row>
     <x:row r="62" ht="19" customHeight="1">
-      <x:c r="A62" s="21"/>
-      <x:c r="B62" s="21"/>
-      <x:c r="C62" s="21"/>
-      <x:c r="D62" s="21"/>
-      <x:c r="E62" s="21"/>
-      <x:c r="F62" s="21"/>
-      <x:c r="G62" s="21"/>
-      <x:c r="H62" s="21"/>
-      <x:c r="I62" s="21"/>
-      <x:c r="J62" s="21"/>
-      <x:c r="K62" s="21"/>
-      <x:c r="L62" s="21"/>
-    </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+      <x:c r="A62" s="91" t="str">
+        <x:v>Reported NIM includes fees and other income after funding costs. Regulatory ratios are disclosed figures.</x:v>
+      </x:c>
+      <x:c r="B62" s="91"/>
+      <x:c r="C62" s="91"/>
+      <x:c r="D62" s="91"/>
+      <x:c r="E62" s="91"/>
+      <x:c r="F62" s="91"/>
+      <x:c r="G62" s="91"/>
+      <x:c r="H62" s="91"/>
+      <x:c r="I62" s="91"/>
+      <x:c r="J62" s="91"/>
+      <x:c r="K62" s="91"/>
+      <x:c r="L62" s="91"/>
+    </x:row>
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -12796,7 +12838,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -12810,7 +12852,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -13875,9 +13917,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A61:G61"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -13900,23 +13939,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Historical Analysis</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -13946,7 +13985,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -13986,7 +14025,7 @@
       <x:c r="K5" s="32"/>
       <x:c r="L5" s="32"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -14310,7 +14349,7 @@
       <x:c r="K16" s="21"/>
       <x:c r="L16" s="21"/>
     </x:row>
-    <x:row r="17" ht="19" customHeight="1">
+    <x:row r="17" ht="8" customHeight="1">
       <x:c r="A17" s="21"/>
       <x:c r="B17" s="21"/>
       <x:c r="C17" s="21"/>
@@ -14324,7 +14363,7 @@
       <x:c r="K17" s="21"/>
       <x:c r="L17" s="21"/>
     </x:row>
-    <x:row r="18" ht="19" customHeight="1">
+    <x:row r="18" ht="8" customHeight="1">
       <x:c r="A18" s="21"/>
       <x:c r="B18" s="21"/>
       <x:c r="C18" s="21"/>
@@ -14338,7 +14377,7 @@
       <x:c r="K18" s="21"/>
       <x:c r="L18" s="21"/>
     </x:row>
-    <x:row r="19" ht="19" customHeight="1">
+    <x:row r="19" ht="8" customHeight="1">
       <x:c r="A19" s="21"/>
       <x:c r="B19" s="21"/>
       <x:c r="C19" s="21"/>
@@ -14352,7 +14391,7 @@
       <x:c r="K19" s="21"/>
       <x:c r="L19" s="21"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20" s="21"/>
       <x:c r="B20" s="21"/>
       <x:c r="C20" s="21"/>
@@ -14366,7 +14405,7 @@
       <x:c r="K20" s="21"/>
       <x:c r="L20" s="21"/>
     </x:row>
-    <x:row r="21" ht="19" customHeight="1">
+    <x:row r="21" ht="8" customHeight="1">
       <x:c r="A21" s="21"/>
       <x:c r="B21" s="21"/>
       <x:c r="C21" s="21"/>
@@ -14380,23 +14419,23 @@
       <x:c r="K21" s="21"/>
       <x:c r="L21" s="21"/>
     </x:row>
-    <x:row r="22" ht="42" customHeight="1">
-      <x:c r="A22" s="36" t="str">
-        <x:v>Credit cost / average net loans uses two year-end balances. Management NIM, ROA and credit-cost guidance use a different average-asset base; those definitions are not interchangeable.</x:v>
-      </x:c>
-      <x:c r="B22" s="36"/>
-      <x:c r="C22" s="36"/>
-      <x:c r="D22" s="36"/>
-      <x:c r="E22" s="36"/>
-      <x:c r="F22" s="36"/>
-      <x:c r="G22" s="36"/>
-      <x:c r="H22" s="36"/>
-      <x:c r="I22" s="36"/>
-      <x:c r="J22" s="36"/>
-      <x:c r="K22" s="36"/>
-      <x:c r="L22" s="36"/>
-    </x:row>
-    <x:row r="23" ht="19" customHeight="1">
+    <x:row r="22" ht="19" customHeight="1">
+      <x:c r="A22" s="91" t="str">
+        <x:v>Historical credit cost uses average net loans. Management guidance uses a different average-asset base.</x:v>
+      </x:c>
+      <x:c r="B22" s="91"/>
+      <x:c r="C22" s="91"/>
+      <x:c r="D22" s="91"/>
+      <x:c r="E22" s="91"/>
+      <x:c r="F22" s="91"/>
+      <x:c r="G22" s="91"/>
+      <x:c r="H22" s="91"/>
+      <x:c r="I22" s="91"/>
+      <x:c r="J22" s="91"/>
+      <x:c r="K22" s="91"/>
+      <x:c r="L22" s="91"/>
+    </x:row>
+    <x:row r="23" ht="8" customHeight="1">
       <x:c r="A23" s="21"/>
       <x:c r="B23" s="21"/>
       <x:c r="C23" s="21"/>
@@ -14410,7 +14449,7 @@
       <x:c r="K23" s="21"/>
       <x:c r="L23" s="21"/>
     </x:row>
-    <x:row r="24" ht="19" customHeight="1">
+    <x:row r="24" ht="8" customHeight="1">
       <x:c r="A24" s="21"/>
       <x:c r="B24" s="21"/>
       <x:c r="C24" s="21"/>
@@ -14424,7 +14463,7 @@
       <x:c r="K24" s="21"/>
       <x:c r="L24" s="21"/>
     </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25" s="21"/>
       <x:c r="B25" s="21"/>
       <x:c r="C25" s="21"/>
@@ -14438,7 +14477,7 @@
       <x:c r="K25" s="21"/>
       <x:c r="L25" s="21"/>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26" s="21"/>
       <x:c r="B26" s="21"/>
       <x:c r="C26" s="21"/>
@@ -14452,7 +14491,7 @@
       <x:c r="K26" s="21"/>
       <x:c r="L26" s="21"/>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27" s="21"/>
       <x:c r="B27" s="21"/>
       <x:c r="C27" s="21"/>
@@ -14466,7 +14505,7 @@
       <x:c r="K27" s="21"/>
       <x:c r="L27" s="21"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="21"/>
       <x:c r="B28" s="21"/>
       <x:c r="C28" s="21"/>
@@ -14480,7 +14519,7 @@
       <x:c r="K28" s="21"/>
       <x:c r="L28" s="21"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29" s="21"/>
       <x:c r="B29" s="21"/>
       <x:c r="C29" s="21"/>
@@ -14494,7 +14533,7 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30" s="21"/>
       <x:c r="B30" s="21"/>
       <x:c r="C30" s="21"/>
@@ -14508,7 +14547,7 @@
       <x:c r="K30" s="21"/>
       <x:c r="L30" s="21"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="21"/>
       <x:c r="C31" s="21"/>
@@ -14522,7 +14561,7 @@
       <x:c r="K31" s="21"/>
       <x:c r="L31" s="21"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="21"/>
       <x:c r="B32" s="21"/>
       <x:c r="C32" s="21"/>
@@ -14536,7 +14575,7 @@
       <x:c r="K32" s="21"/>
       <x:c r="L32" s="21"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="21"/>
       <x:c r="B33" s="21"/>
       <x:c r="C33" s="21"/>
@@ -14550,7 +14589,7 @@
       <x:c r="K33" s="21"/>
       <x:c r="L33" s="21"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34" s="21"/>
       <x:c r="B34" s="21"/>
       <x:c r="C34" s="21"/>
@@ -14564,7 +14603,7 @@
       <x:c r="K34" s="21"/>
       <x:c r="L34" s="21"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="21"/>
       <x:c r="B35" s="21"/>
       <x:c r="C35" s="21"/>
@@ -14578,7 +14617,7 @@
       <x:c r="K35" s="21"/>
       <x:c r="L35" s="21"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="21"/>
       <x:c r="B36" s="21"/>
       <x:c r="C36" s="21"/>
@@ -14592,7 +14631,7 @@
       <x:c r="K36" s="21"/>
       <x:c r="L36" s="21"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="21"/>
       <x:c r="B37" s="21"/>
       <x:c r="C37" s="21"/>
@@ -14606,7 +14645,7 @@
       <x:c r="K37" s="21"/>
       <x:c r="L37" s="21"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="21"/>
       <x:c r="C38" s="21"/>
@@ -14620,7 +14659,7 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="21"/>
       <x:c r="C39" s="21"/>
@@ -14634,7 +14673,7 @@
       <x:c r="K39" s="21"/>
       <x:c r="L39" s="21"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -14648,7 +14687,7 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -14662,7 +14701,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -14676,7 +14715,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -14690,7 +14729,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -14704,7 +14743,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -14718,7 +14757,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -14732,7 +14771,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -14746,7 +14785,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -14760,7 +14799,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -14774,7 +14813,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -14788,7 +14827,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -14802,7 +14841,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -14816,7 +14855,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -14830,7 +14869,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -14844,7 +14883,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -14858,7 +14897,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -14872,7 +14911,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -14886,7 +14925,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -14900,7 +14939,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -14914,7 +14953,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -14928,7 +14967,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -14942,7 +14981,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -14956,7 +14995,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -14970,7 +15009,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -14984,7 +15023,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -16049,9 +16088,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A22:G22"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -16074,23 +16110,23 @@
     <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="92" t="str">
         <x:v>Industry and Business Context</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="29"/>
-      <x:c r="D1" s="29"/>
-      <x:c r="E1" s="29"/>
-      <x:c r="F1" s="29"/>
-      <x:c r="G1" s="29"/>
-      <x:c r="H1" s="29"/>
-      <x:c r="I1" s="29"/>
-      <x:c r="J1" s="29"/>
-      <x:c r="K1" s="29"/>
-      <x:c r="L1" s="29"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="92"/>
+      <x:c r="C1" s="93"/>
+      <x:c r="D1" s="93"/>
+      <x:c r="E1" s="93"/>
+      <x:c r="F1" s="93"/>
+      <x:c r="G1" s="93"/>
+      <x:c r="H1" s="93"/>
+      <x:c r="I1" s="93"/>
+      <x:c r="J1" s="93"/>
+      <x:c r="K1" s="93"/>
+      <x:c r="L1" s="93"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -16120,7 +16156,7 @@
       <x:c r="K3" s="2"/>
       <x:c r="L3" s="2"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -16154,7 +16190,7 @@
       <x:c r="K5"/>
       <x:c r="L5"/>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6"/>
       <x:c r="B6"/>
       <x:c r="C6"/>
@@ -16188,7 +16224,7 @@
       <x:c r="K7"/>
       <x:c r="L7"/>
     </x:row>
-    <x:row r="8" ht="19" customHeight="1">
+    <x:row r="8" ht="8" customHeight="1">
       <x:c r="A8"/>
       <x:c r="B8"/>
       <x:c r="C8"/>
@@ -16202,7 +16238,7 @@
       <x:c r="K8"/>
       <x:c r="L8"/>
     </x:row>
-    <x:row r="9" ht="19" customHeight="1">
+    <x:row r="9" ht="8" customHeight="1">
       <x:c r="A9"/>
       <x:c r="B9"/>
       <x:c r="C9"/>
@@ -16236,7 +16272,7 @@
       <x:c r="K10"/>
       <x:c r="L10"/>
     </x:row>
-    <x:row r="11" ht="19" customHeight="1">
+    <x:row r="11" ht="8" customHeight="1">
       <x:c r="A11"/>
       <x:c r="B11"/>
       <x:c r="C11"/>
@@ -16250,7 +16286,7 @@
       <x:c r="K11"/>
       <x:c r="L11"/>
     </x:row>
-    <x:row r="12" ht="19" customHeight="1">
+    <x:row r="12" ht="8" customHeight="1">
       <x:c r="A12"/>
       <x:c r="B12"/>
       <x:c r="C12"/>
@@ -16284,7 +16320,7 @@
       <x:c r="K13"/>
       <x:c r="L13"/>
     </x:row>
-    <x:row r="14" ht="19" customHeight="1">
+    <x:row r="14" ht="8" customHeight="1">
       <x:c r="A14"/>
       <x:c r="B14"/>
       <x:c r="C14"/>
@@ -16298,7 +16334,7 @@
       <x:c r="K14"/>
       <x:c r="L14"/>
     </x:row>
-    <x:row r="15" ht="19" customHeight="1">
+    <x:row r="15" ht="8" customHeight="1">
       <x:c r="A15"/>
       <x:c r="B15"/>
       <x:c r="C15"/>
@@ -16332,7 +16368,7 @@
       <x:c r="K16"/>
       <x:c r="L16"/>
     </x:row>
-    <x:row r="17" ht="19" customHeight="1">
+    <x:row r="17" ht="8" customHeight="1">
       <x:c r="A17"/>
       <x:c r="B17"/>
       <x:c r="C17"/>
@@ -16346,7 +16382,7 @@
       <x:c r="K17"/>
       <x:c r="L17"/>
     </x:row>
-    <x:row r="18" ht="19" customHeight="1">
+    <x:row r="18" ht="8" customHeight="1">
       <x:c r="A18"/>
       <x:c r="B18"/>
       <x:c r="C18"/>
@@ -16380,7 +16416,7 @@
       <x:c r="K19"/>
       <x:c r="L19"/>
     </x:row>
-    <x:row r="20" ht="19" customHeight="1">
+    <x:row r="20" ht="8" customHeight="1">
       <x:c r="A20"/>
       <x:c r="B20"/>
       <x:c r="C20"/>
@@ -16394,7 +16430,7 @@
       <x:c r="K20"/>
       <x:c r="L20"/>
     </x:row>
-    <x:row r="21" ht="19" customHeight="1">
+    <x:row r="21" ht="8" customHeight="1">
       <x:c r="A21"/>
       <x:c r="B21"/>
       <x:c r="C21"/>
@@ -16428,7 +16464,7 @@
       <x:c r="K22"/>
       <x:c r="L22"/>
     </x:row>
-    <x:row r="23" ht="19" customHeight="1">
+    <x:row r="23" ht="8" customHeight="1">
       <x:c r="A23"/>
       <x:c r="B23"/>
       <x:c r="C23"/>
@@ -16442,7 +16478,7 @@
       <x:c r="K23"/>
       <x:c r="L23"/>
     </x:row>
-    <x:row r="24" ht="19" customHeight="1">
+    <x:row r="24" ht="8" customHeight="1">
       <x:c r="A24"/>
       <x:c r="B24"/>
       <x:c r="C24"/>
@@ -16456,7 +16492,7 @@
       <x:c r="K24"/>
       <x:c r="L24"/>
     </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25"/>
       <x:c r="B25"/>
       <x:c r="C25"/>
@@ -16470,7 +16506,7 @@
       <x:c r="K25"/>
       <x:c r="L25"/>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26"/>
       <x:c r="B26"/>
       <x:c r="C26"/>
@@ -16484,7 +16520,7 @@
       <x:c r="K26"/>
       <x:c r="L26"/>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27"/>
       <x:c r="B27"/>
       <x:c r="C27"/>
@@ -16498,7 +16534,7 @@
       <x:c r="K27"/>
       <x:c r="L27"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28"/>
       <x:c r="B28"/>
       <x:c r="C28"/>
@@ -16512,7 +16548,7 @@
       <x:c r="K28"/>
       <x:c r="L28"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29"/>
       <x:c r="B29"/>
       <x:c r="C29"/>
@@ -16526,7 +16562,7 @@
       <x:c r="K29"/>
       <x:c r="L29"/>
     </x:row>
-    <x:row r="30" ht="30" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30"/>
       <x:c r="B30"/>
       <x:c r="C30"/>
@@ -16540,7 +16576,7 @@
       <x:c r="K30"/>
       <x:c r="L30"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31"/>
       <x:c r="B31"/>
       <x:c r="C31"/>
@@ -16554,7 +16590,7 @@
       <x:c r="K31"/>
       <x:c r="L31"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32"/>
       <x:c r="B32"/>
       <x:c r="C32"/>
@@ -16568,7 +16604,7 @@
       <x:c r="K32"/>
       <x:c r="L32"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33"/>
       <x:c r="B33"/>
       <x:c r="C33"/>
@@ -16582,7 +16618,7 @@
       <x:c r="K33"/>
       <x:c r="L33"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34"/>
       <x:c r="B34"/>
       <x:c r="C34"/>
@@ -16596,7 +16632,7 @@
       <x:c r="K34"/>
       <x:c r="L34"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35"/>
       <x:c r="B35"/>
       <x:c r="C35"/>
@@ -16610,7 +16646,7 @@
       <x:c r="K35"/>
       <x:c r="L35"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="2"/>
       <x:c r="B36" s="2"/>
       <x:c r="C36" s="2"/>
@@ -16624,7 +16660,7 @@
       <x:c r="K36" s="2"/>
       <x:c r="L36" s="2"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
@@ -16638,7 +16674,7 @@
       <x:c r="K37" s="2"/>
       <x:c r="L37" s="2"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="2"/>
       <x:c r="B38" s="2"/>
       <x:c r="C38" s="2"/>
@@ -16652,7 +16688,7 @@
       <x:c r="K38" s="2"/>
       <x:c r="L38" s="2"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="2"/>
       <x:c r="B39" s="2"/>
       <x:c r="C39" s="2"/>
@@ -16666,7 +16702,7 @@
       <x:c r="K39" s="2"/>
       <x:c r="L39" s="2"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="2"/>
       <x:c r="B40" s="2"/>
       <x:c r="C40" s="2"/>
@@ -16680,7 +16716,7 @@
       <x:c r="K40" s="2"/>
       <x:c r="L40" s="2"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="2"/>
       <x:c r="B41" s="2"/>
       <x:c r="C41" s="2"/>
@@ -16694,7 +16730,7 @@
       <x:c r="K41" s="2"/>
       <x:c r="L41" s="2"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="2"/>
       <x:c r="B42" s="2"/>
       <x:c r="C42" s="2"/>
@@ -16708,7 +16744,7 @@
       <x:c r="K42" s="2"/>
       <x:c r="L42" s="2"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="2"/>
       <x:c r="B43" s="2"/>
       <x:c r="C43" s="2"/>
@@ -16722,7 +16758,7 @@
       <x:c r="K43" s="2"/>
       <x:c r="L43" s="2"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="2"/>
       <x:c r="B44" s="2"/>
       <x:c r="C44" s="2"/>
@@ -16736,7 +16772,7 @@
       <x:c r="K44" s="2"/>
       <x:c r="L44" s="2"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="2"/>
       <x:c r="B45" s="2"/>
       <x:c r="C45" s="2"/>
@@ -16750,7 +16786,7 @@
       <x:c r="K45" s="2"/>
       <x:c r="L45" s="2"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="2"/>
       <x:c r="B46" s="2"/>
       <x:c r="C46" s="2"/>
@@ -16764,7 +16800,7 @@
       <x:c r="K46" s="2"/>
       <x:c r="L46" s="2"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="2"/>
       <x:c r="B47" s="2"/>
       <x:c r="C47" s="2"/>
@@ -16778,7 +16814,7 @@
       <x:c r="K47" s="2"/>
       <x:c r="L47" s="2"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="2"/>
       <x:c r="B48" s="2"/>
       <x:c r="C48" s="2"/>
@@ -16792,7 +16828,7 @@
       <x:c r="K48" s="2"/>
       <x:c r="L48" s="2"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="2"/>
       <x:c r="B49" s="2"/>
       <x:c r="C49" s="2"/>
@@ -16806,7 +16842,7 @@
       <x:c r="K49" s="2"/>
       <x:c r="L49" s="2"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="2"/>
       <x:c r="B50" s="2"/>
       <x:c r="C50" s="2"/>
@@ -16820,7 +16856,7 @@
       <x:c r="K50" s="2"/>
       <x:c r="L50" s="2"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="2"/>
       <x:c r="B51" s="2"/>
       <x:c r="C51" s="2"/>
@@ -16834,7 +16870,7 @@
       <x:c r="K51" s="2"/>
       <x:c r="L51" s="2"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="2"/>
       <x:c r="B52" s="2"/>
       <x:c r="C52" s="2"/>
@@ -16848,7 +16884,7 @@
       <x:c r="K52" s="2"/>
       <x:c r="L52" s="2"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="2"/>
       <x:c r="B53" s="2"/>
       <x:c r="C53" s="2"/>
@@ -16862,7 +16898,7 @@
       <x:c r="K53" s="2"/>
       <x:c r="L53" s="2"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="2"/>
       <x:c r="B54" s="2"/>
       <x:c r="C54" s="2"/>
@@ -16876,7 +16912,7 @@
       <x:c r="K54" s="2"/>
       <x:c r="L54" s="2"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="2"/>
       <x:c r="B55" s="2"/>
       <x:c r="C55" s="2"/>
@@ -16890,7 +16926,7 @@
       <x:c r="K55" s="2"/>
       <x:c r="L55" s="2"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="2"/>
       <x:c r="B56" s="2"/>
       <x:c r="C56" s="2"/>
@@ -16904,7 +16940,7 @@
       <x:c r="K56" s="2"/>
       <x:c r="L56" s="2"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="2"/>
       <x:c r="B57" s="2"/>
       <x:c r="C57" s="2"/>
@@ -16918,7 +16954,7 @@
       <x:c r="K57" s="2"/>
       <x:c r="L57" s="2"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="2"/>
       <x:c r="B58" s="2"/>
       <x:c r="C58" s="2"/>
@@ -16932,7 +16968,7 @@
       <x:c r="K58" s="2"/>
       <x:c r="L58" s="2"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="2"/>
       <x:c r="B59" s="2"/>
       <x:c r="C59" s="2"/>
@@ -16946,7 +16982,7 @@
       <x:c r="K59" s="2"/>
       <x:c r="L59" s="2"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="2"/>
       <x:c r="B60" s="2"/>
       <x:c r="C60" s="2"/>
@@ -16960,7 +16996,7 @@
       <x:c r="K60" s="2"/>
       <x:c r="L60" s="2"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="2"/>
       <x:c r="B61" s="2"/>
       <x:c r="C61" s="2"/>
@@ -16974,7 +17010,7 @@
       <x:c r="K61" s="2"/>
       <x:c r="L61" s="2"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="2"/>
       <x:c r="B62" s="2"/>
       <x:c r="C62" s="2"/>
@@ -16988,7 +17024,7 @@
       <x:c r="K62" s="2"/>
       <x:c r="L62" s="2"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="2"/>
       <x:c r="B63" s="2"/>
       <x:c r="C63" s="2"/>
@@ -17002,7 +17038,7 @@
       <x:c r="K63" s="2"/>
       <x:c r="L63" s="2"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="2"/>
       <x:c r="B64" s="2"/>
       <x:c r="C64" s="2"/>
@@ -17016,7 +17052,7 @@
       <x:c r="K64" s="2"/>
       <x:c r="L64" s="2"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="2"/>
       <x:c r="B65" s="2"/>
       <x:c r="C65" s="2"/>
@@ -18103,23 +18139,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Forecast Assumptions</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -18149,7 +18185,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -18199,7 +18235,7 @@
         <x:v>FY2031E</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -18944,7 +18980,7 @@
         <x:v>0.0013183805645248215</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26"/>
       <x:c r="B26"/>
       <x:c r="C26"/>
@@ -18958,7 +18994,7 @@
       <x:c r="K26"/>
       <x:c r="L26"/>
     </x:row>
-    <x:row r="27" ht="30" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27"/>
       <x:c r="B27"/>
       <x:c r="C27"/>
@@ -18972,83 +19008,87 @@
       <x:c r="K27"/>
       <x:c r="L27"/>
     </x:row>
-    <x:row r="28" ht="42" customHeight="1">
-      <x:c r="A28" s="52" t="str">
-        <x:v>Management commentary, May 2026: growth 20%-23%, NIM around 8%, operating costs 3.0%-3.1%, credit cost about 1.5%, pre-tax ROA around 3.5%. July call maintained growth at 22%-23% and credit cost at 1.5%.</x:v>
-      </x:c>
-      <x:c r="B28" s="52"/>
-      <x:c r="C28" s="52"/>
-      <x:c r="D28" s="52"/>
-      <x:c r="E28" s="52"/>
-      <x:c r="F28" s="52"/>
-      <x:c r="G28" s="52"/>
-      <x:c r="H28" s="52"/>
-      <x:c r="I28" s="52"/>
-      <x:c r="J28" s="52"/>
-      <x:c r="K28" s="52"/>
-      <x:c r="L28" s="52"/>
-    </x:row>
-    <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29"/>
-      <x:c r="B29"/>
-      <x:c r="C29"/>
-      <x:c r="D29"/>
-      <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-      <x:c r="I29"/>
-      <x:c r="J29"/>
-      <x:c r="K29"/>
-      <x:c r="L29"/>
-    </x:row>
-    <x:row r="30" ht="42" customHeight="1">
-      <x:c r="A30" s="52" t="str">
-        <x:v>Management commentary, FY2026 MDA and July call: funding cost was 7.5% in FY2026 and should be broadly flat in FY2027, with possible second-half pressure. Model uses 7.5%, then 7.6%.</x:v>
-      </x:c>
-      <x:c r="B30" s="52"/>
-      <x:c r="C30" s="52"/>
-      <x:c r="D30" s="52"/>
-      <x:c r="E30" s="52"/>
-      <x:c r="F30" s="52"/>
-      <x:c r="G30" s="52"/>
-      <x:c r="H30" s="52"/>
-      <x:c r="I30" s="52"/>
-      <x:c r="J30" s="52"/>
-      <x:c r="K30" s="52"/>
-      <x:c r="L30" s="52"/>
+    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A28" s="91" t="str">
+        <x:v>Management guidance (May 2026): growth 20–23%, NIM 8%, opex 3–3.1%, credit cost 1.5%, pre-tax ROA 3.5%.</x:v>
+      </x:c>
+      <x:c r="B28" s="91"/>
+      <x:c r="C28" s="91"/>
+      <x:c r="D28" s="91"/>
+      <x:c r="E28" s="91"/>
+      <x:c r="F28" s="91"/>
+      <x:c r="G28" s="91"/>
+      <x:c r="H28" s="91"/>
+      <x:c r="I28" s="91"/>
+      <x:c r="J28" s="91"/>
+      <x:c r="K28" s="91"/>
+      <x:c r="L28" s="91"/>
+    </x:row>
+    <x:row r="29" ht="19" customHeight="1">
+      <x:c r="A29" s="91" t="str">
+        <x:v>Management guidance (July 2026): growth 22–23% and credit cost 1.5%.</x:v>
+      </x:c>
+      <x:c r="B29" s="91"/>
+      <x:c r="C29" s="91"/>
+      <x:c r="D29" s="91"/>
+      <x:c r="E29" s="91"/>
+      <x:c r="F29" s="91"/>
+      <x:c r="G29" s="91"/>
+      <x:c r="H29" s="91"/>
+      <x:c r="I29" s="91"/>
+      <x:c r="J29" s="91"/>
+      <x:c r="K29" s="91"/>
+      <x:c r="L29" s="91"/>
+    </x:row>
+    <x:row r="30" ht="19" customHeight="1">
+      <x:c r="A30" s="91" t="str">
+        <x:v>Management commentary: FY2026 funding cost 7.5%. FY2027 remains flat with potential upward pressure.</x:v>
+      </x:c>
+      <x:c r="B30" s="91"/>
+      <x:c r="C30" s="91"/>
+      <x:c r="D30" s="91"/>
+      <x:c r="E30" s="91"/>
+      <x:c r="F30" s="91"/>
+      <x:c r="G30" s="91"/>
+      <x:c r="H30" s="91"/>
+      <x:c r="I30" s="91"/>
+      <x:c r="J30" s="91"/>
+      <x:c r="K30" s="91"/>
+      <x:c r="L30" s="91"/>
     </x:row>
     <x:row r="31" ht="19" customHeight="1">
-      <x:c r="A31"/>
-      <x:c r="B31"/>
-      <x:c r="C31"/>
-      <x:c r="D31"/>
-      <x:c r="E31"/>
-      <x:c r="F31"/>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-      <x:c r="I31"/>
-      <x:c r="J31"/>
-      <x:c r="K31"/>
-      <x:c r="L31"/>
-    </x:row>
-    <x:row r="32" ht="42" customHeight="1">
-      <x:c r="A32" s="52" t="str">
-        <x:v>FY2028-FY2031 growth fades to 16%. Flat 8% net income margin, 3.05% costs and 1.5% credit losses imply 3.45% pre-tax return on the model asset base. These later-year extensions are analyst assumptions.</x:v>
-      </x:c>
-      <x:c r="B32" s="52"/>
-      <x:c r="C32" s="52"/>
-      <x:c r="D32" s="52"/>
-      <x:c r="E32" s="52"/>
-      <x:c r="F32" s="52"/>
-      <x:c r="G32" s="52"/>
-      <x:c r="H32" s="52"/>
-      <x:c r="I32" s="52"/>
-      <x:c r="J32" s="52"/>
-      <x:c r="K32" s="52"/>
-      <x:c r="L32" s="52"/>
-    </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+      <x:c r="A31" s="91" t="str">
+        <x:v>Model funding cost: 7.5%, then 7.6%. Later-year growth fades to 16%. These are analyst assumptions.</x:v>
+      </x:c>
+      <x:c r="B31" s="91"/>
+      <x:c r="C31" s="91"/>
+      <x:c r="D31" s="91"/>
+      <x:c r="E31" s="91"/>
+      <x:c r="F31" s="91"/>
+      <x:c r="G31" s="91"/>
+      <x:c r="H31" s="91"/>
+      <x:c r="I31" s="91"/>
+      <x:c r="J31" s="91"/>
+      <x:c r="K31" s="91"/>
+      <x:c r="L31" s="91"/>
+    </x:row>
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" s="91" t="str">
+        <x:v>Later-year net income, opex and credit-cost ratios remain flat. Implied pre-tax ROA is about 3.45%.</x:v>
+      </x:c>
+      <x:c r="B32" s="91"/>
+      <x:c r="C32" s="91"/>
+      <x:c r="D32" s="91"/>
+      <x:c r="E32" s="91"/>
+      <x:c r="F32" s="91"/>
+      <x:c r="G32" s="91"/>
+      <x:c r="H32" s="91"/>
+      <x:c r="I32" s="91"/>
+      <x:c r="J32" s="91"/>
+      <x:c r="K32" s="91"/>
+      <x:c r="L32" s="91"/>
+    </x:row>
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33"/>
       <x:c r="B33"/>
       <x:c r="C33"/>
@@ -19062,67 +19102,71 @@
       <x:c r="K33"/>
       <x:c r="L33"/>
     </x:row>
-    <x:row r="34" ht="42" customHeight="1">
-      <x:c r="A34" s="52" t="str">
-        <x:v>Asset base is a proxy calibrated from FY2026 net income / reported 8% NIM, then held proportional to average net loans. It approximates management reporting averages; it is not balance-sheet total assets.</x:v>
-      </x:c>
-      <x:c r="B34" s="52"/>
-      <x:c r="C34" s="52"/>
-      <x:c r="D34" s="52"/>
-      <x:c r="E34" s="52"/>
-      <x:c r="F34" s="52"/>
-      <x:c r="G34" s="52"/>
-      <x:c r="H34" s="52"/>
-      <x:c r="I34" s="52"/>
-      <x:c r="J34" s="52"/>
-      <x:c r="K34" s="52"/>
-      <x:c r="L34" s="52"/>
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" s="91" t="str">
+        <x:v>Average-asset base: FY2026 net income divided by 8%, then held proportional to average net loans.</x:v>
+      </x:c>
+      <x:c r="B34" s="91"/>
+      <x:c r="C34" s="91"/>
+      <x:c r="D34" s="91"/>
+      <x:c r="E34" s="91"/>
+      <x:c r="F34" s="91"/>
+      <x:c r="G34" s="91"/>
+      <x:c r="H34" s="91"/>
+      <x:c r="I34" s="91"/>
+      <x:c r="J34" s="91"/>
+      <x:c r="K34" s="91"/>
+      <x:c r="L34" s="91"/>
     </x:row>
     <x:row r="35" ht="19" customHeight="1">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-      <x:c r="I35"/>
-      <x:c r="J35"/>
-      <x:c r="K35"/>
-      <x:c r="L35"/>
-    </x:row>
-    <x:row r="36" ht="42" customHeight="1">
-      <x:c r="A36" s="52" t="str">
-        <x:v>14% book equity / net loans is a capital-intensity assumption close to FY2026. It is not regulatory CAR. Discount rate, terminal growth and terminal ROE are valuation assumptions, not management guidance.</x:v>
-      </x:c>
-      <x:c r="B36" s="52"/>
-      <x:c r="C36" s="52"/>
-      <x:c r="D36" s="52"/>
-      <x:c r="E36" s="52"/>
-      <x:c r="F36" s="52"/>
-      <x:c r="G36" s="52"/>
-      <x:c r="H36" s="52"/>
-      <x:c r="I36" s="52"/>
-      <x:c r="J36" s="52"/>
-      <x:c r="K36" s="52"/>
-      <x:c r="L36" s="52"/>
+      <x:c r="A35" s="91" t="str">
+        <x:v>This calibrated base is used for management operating ratios. It is not balance-sheet total assets.</x:v>
+      </x:c>
+      <x:c r="B35" s="91"/>
+      <x:c r="C35" s="91"/>
+      <x:c r="D35" s="91"/>
+      <x:c r="E35" s="91"/>
+      <x:c r="F35" s="91"/>
+      <x:c r="G35" s="91"/>
+      <x:c r="H35" s="91"/>
+      <x:c r="I35" s="91"/>
+      <x:c r="J35" s="91"/>
+      <x:c r="K35" s="91"/>
+      <x:c r="L35" s="91"/>
+    </x:row>
+    <x:row r="36" ht="19" customHeight="1">
+      <x:c r="A36" s="91" t="str">
+        <x:v>Required book equity is 14% of net loans, close to the actual level. It is not regulatory capital adequacy.</x:v>
+      </x:c>
+      <x:c r="B36" s="91"/>
+      <x:c r="C36" s="91"/>
+      <x:c r="D36" s="91"/>
+      <x:c r="E36" s="91"/>
+      <x:c r="F36" s="91"/>
+      <x:c r="G36" s="91"/>
+      <x:c r="H36" s="91"/>
+      <x:c r="I36" s="91"/>
+      <x:c r="J36" s="91"/>
+      <x:c r="K36" s="91"/>
+      <x:c r="L36" s="91"/>
     </x:row>
     <x:row r="37" ht="19" customHeight="1">
-      <x:c r="A37"/>
-      <x:c r="B37"/>
-      <x:c r="C37"/>
-      <x:c r="D37"/>
-      <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-      <x:c r="I37"/>
-      <x:c r="J37"/>
-      <x:c r="K37"/>
-      <x:c r="L37"/>
-    </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A37" s="91" t="str">
+        <x:v>Cost of equity, terminal growth and terminal ROE are valuation assumptions, not management guidance.</x:v>
+      </x:c>
+      <x:c r="B37" s="91"/>
+      <x:c r="C37" s="91"/>
+      <x:c r="D37" s="91"/>
+      <x:c r="E37" s="91"/>
+      <x:c r="F37" s="91"/>
+      <x:c r="G37" s="91"/>
+      <x:c r="H37" s="91"/>
+      <x:c r="I37" s="91"/>
+      <x:c r="J37" s="91"/>
+      <x:c r="K37" s="91"/>
+      <x:c r="L37" s="91"/>
+    </x:row>
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38"/>
       <x:c r="B38"/>
       <x:c r="C38"/>
@@ -19301,7 +19345,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -19315,23 +19359,23 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="42" customHeight="1">
-      <x:c r="A49" s="36" t="str">
-        <x:v>CCD dilution uses the contractual floor less the maximum 5% discount, a conservative estimate. Rs 630 crore converts from debt to equity in FY2027; actual conversion prices may differ.</x:v>
-      </x:c>
-      <x:c r="B49" s="36"/>
-      <x:c r="C49" s="36"/>
-      <x:c r="D49" s="36"/>
-      <x:c r="E49" s="36"/>
-      <x:c r="F49" s="36"/>
-      <x:c r="G49" s="36"/>
-      <x:c r="H49" s="36"/>
-      <x:c r="I49" s="36"/>
-      <x:c r="J49" s="36"/>
-      <x:c r="K49" s="36"/>
-      <x:c r="L49" s="36"/>
-    </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="49" ht="19" customHeight="1">
+      <x:c r="A49" s="91" t="str">
+        <x:v>FY2027 CCD conversion: ₹630 crore at an assumed ₹1,140.48 per share (floor less 5%). Actual pricing may differ.</x:v>
+      </x:c>
+      <x:c r="B49" s="91"/>
+      <x:c r="C49" s="91"/>
+      <x:c r="D49" s="91"/>
+      <x:c r="E49" s="91"/>
+      <x:c r="F49" s="91"/>
+      <x:c r="G49" s="91"/>
+      <x:c r="H49" s="91"/>
+      <x:c r="I49" s="91"/>
+      <x:c r="J49" s="91"/>
+      <x:c r="K49" s="91"/>
+      <x:c r="L49" s="91"/>
+    </x:row>
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -19345,7 +19389,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -19359,7 +19403,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -19373,7 +19417,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -19387,7 +19431,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -19401,7 +19445,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -19415,7 +19459,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -19429,7 +19473,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -19443,7 +19487,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -19457,7 +19501,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -19471,7 +19515,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -19485,7 +19529,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -19499,7 +19543,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -19513,7 +19557,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -19527,7 +19571,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -19541,7 +19585,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -20606,14 +20650,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A28:L28"/>
-    <x:mergeCell ref="A30:L30"/>
-    <x:mergeCell ref="A32:L32"/>
-    <x:mergeCell ref="A34:L34"/>
-    <x:mergeCell ref="A36:L36"/>
-    <x:mergeCell ref="A49:L49"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -20636,23 +20672,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Lending and Capital Schedules</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -20682,7 +20718,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -20732,7 +20768,7 @@
         <x:v>FY2031E</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -21084,7 +21120,7 @@
         <x:v>507347.94412058475</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="19" customHeight="1">
+    <x:row r="15" ht="8" customHeight="1">
       <x:c r="A15" s="21"/>
       <x:c r="B15" s="21"/>
       <x:c r="C15" s="21"/>
@@ -21574,7 +21610,7 @@
         <x:v>13097.872097197458</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27" s="21"/>
       <x:c r="B27" s="21"/>
       <x:c r="C27" s="21"/>
@@ -21588,7 +21624,7 @@
       <x:c r="K27" s="21"/>
       <x:c r="L27" s="21"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="21"/>
       <x:c r="B28" s="21"/>
       <x:c r="C28" s="21"/>
@@ -22058,7 +22094,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -22072,37 +22108,39 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="42" customHeight="1">
-      <x:c r="A41" s="36" t="str">
-        <x:v>Net income margin includes non-interest income. Book equity rolls through PAT, dividends, CCD conversion and any funding shortfall. Borrowings fund the remaining assets after other liabilities and equity.</x:v>
-      </x:c>
-      <x:c r="B41" s="36"/>
-      <x:c r="C41" s="36"/>
-      <x:c r="D41" s="36"/>
-      <x:c r="E41" s="36"/>
-      <x:c r="F41" s="36"/>
-      <x:c r="G41" s="36"/>
-      <x:c r="H41" s="36"/>
-      <x:c r="I41" s="36"/>
-      <x:c r="J41" s="36"/>
-      <x:c r="K41" s="36"/>
-      <x:c r="L41" s="36"/>
+    <x:row r="41" ht="19" customHeight="1">
+      <x:c r="A41" s="91" t="str">
+        <x:v>Net income includes non-interest income. Equity reflects profit, dividends and CCD conversion.</x:v>
+      </x:c>
+      <x:c r="B41" s="91"/>
+      <x:c r="C41" s="91"/>
+      <x:c r="D41" s="91"/>
+      <x:c r="E41" s="91"/>
+      <x:c r="F41" s="91"/>
+      <x:c r="G41" s="91"/>
+      <x:c r="H41" s="91"/>
+      <x:c r="I41" s="91"/>
+      <x:c r="J41" s="91"/>
+      <x:c r="K41" s="91"/>
+      <x:c r="L41" s="91"/>
     </x:row>
     <x:row r="42" ht="19" customHeight="1">
-      <x:c r="A42" s="21"/>
-      <x:c r="B42" s="21"/>
-      <x:c r="C42" s="21"/>
-      <x:c r="D42" s="21"/>
-      <x:c r="E42" s="21"/>
-      <x:c r="F42" s="21"/>
-      <x:c r="G42" s="21"/>
-      <x:c r="H42" s="21"/>
-      <x:c r="I42" s="21"/>
-      <x:c r="J42" s="21"/>
-      <x:c r="K42" s="21"/>
-      <x:c r="L42" s="21"/>
-    </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+      <x:c r="A42" s="91" t="str">
+        <x:v>Borrowings fund the remaining assets after equity and other liabilities.</x:v>
+      </x:c>
+      <x:c r="B42" s="91"/>
+      <x:c r="C42" s="91"/>
+      <x:c r="D42" s="91"/>
+      <x:c r="E42" s="91"/>
+      <x:c r="F42" s="91"/>
+      <x:c r="G42" s="91"/>
+      <x:c r="H42" s="91"/>
+      <x:c r="I42" s="91"/>
+      <x:c r="J42" s="91"/>
+      <x:c r="K42" s="91"/>
+      <x:c r="L42" s="91"/>
+    </x:row>
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -22116,7 +22154,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -22130,7 +22168,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -22144,7 +22182,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -22158,7 +22196,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -22172,7 +22210,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -22186,7 +22224,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -22200,7 +22238,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -22214,7 +22252,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -22228,7 +22266,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -22242,7 +22280,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -22256,7 +22294,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -22270,7 +22308,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -22284,7 +22322,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -22298,7 +22336,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -22312,7 +22350,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -22326,7 +22364,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -22340,7 +22378,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -22354,7 +22392,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -22368,7 +22406,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -22382,7 +22420,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -22396,7 +22434,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -22410,7 +22448,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -23475,9 +23513,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A41:L41"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -23500,23 +23535,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Income Statement</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -23546,7 +23581,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -23596,7 +23631,7 @@
         <x:v>FY2031E</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -24224,7 +24259,7 @@
         <x:v>0.18260395275277166</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="19" customHeight="1">
+    <x:row r="21" ht="8" customHeight="1">
       <x:c r="A21" s="21"/>
       <x:c r="B21" s="21"/>
       <x:c r="C21" s="21"/>
@@ -24238,7 +24273,7 @@
       <x:c r="K21" s="21"/>
       <x:c r="L21" s="21"/>
     </x:row>
-    <x:row r="22" ht="19" customHeight="1">
+    <x:row r="22" ht="8" customHeight="1">
       <x:c r="A22" s="21"/>
       <x:c r="B22" s="21"/>
       <x:c r="C22" s="21"/>
@@ -24252,37 +24287,39 @@
       <x:c r="K22" s="21"/>
       <x:c r="L22" s="21"/>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="36" t="str">
-        <x:v>Historical ROA and ROE are company-reported. Forecast pre-tax ROA uses the calibrated model asset base. Forecast ROE uses average opening and closing book equity.</x:v>
-      </x:c>
-      <x:c r="B23" s="36"/>
-      <x:c r="C23" s="36"/>
-      <x:c r="D23" s="36"/>
-      <x:c r="E23" s="36"/>
-      <x:c r="F23" s="36"/>
-      <x:c r="G23" s="36"/>
-      <x:c r="H23" s="36"/>
-      <x:c r="I23" s="36"/>
-      <x:c r="J23" s="36"/>
-      <x:c r="K23" s="36"/>
-      <x:c r="L23" s="36"/>
+    <x:row r="23" ht="19" customHeight="1">
+      <x:c r="A23" s="91" t="str">
+        <x:v>Historical ROA and ROE are company disclosures. Forecast ROA uses the calibrated average-asset base.</x:v>
+      </x:c>
+      <x:c r="B23" s="91"/>
+      <x:c r="C23" s="91"/>
+      <x:c r="D23" s="91"/>
+      <x:c r="E23" s="91"/>
+      <x:c r="F23" s="91"/>
+      <x:c r="G23" s="91"/>
+      <x:c r="H23" s="91"/>
+      <x:c r="I23" s="91"/>
+      <x:c r="J23" s="91"/>
+      <x:c r="K23" s="91"/>
+      <x:c r="L23" s="91"/>
     </x:row>
     <x:row r="24" ht="19" customHeight="1">
-      <x:c r="A24" s="21"/>
-      <x:c r="B24" s="21"/>
-      <x:c r="C24" s="21"/>
-      <x:c r="D24" s="21"/>
-      <x:c r="E24" s="21"/>
-      <x:c r="F24" s="21"/>
-      <x:c r="G24" s="21"/>
-      <x:c r="H24" s="21"/>
-      <x:c r="I24" s="21"/>
-      <x:c r="J24" s="21"/>
-      <x:c r="K24" s="21"/>
-      <x:c r="L24" s="21"/>
-    </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+      <x:c r="A24" s="91" t="str">
+        <x:v>Forecast ROE uses average book equity.</x:v>
+      </x:c>
+      <x:c r="B24" s="91"/>
+      <x:c r="C24" s="91"/>
+      <x:c r="D24" s="91"/>
+      <x:c r="E24" s="91"/>
+      <x:c r="F24" s="91"/>
+      <x:c r="G24" s="91"/>
+      <x:c r="H24" s="91"/>
+      <x:c r="I24" s="91"/>
+      <x:c r="J24" s="91"/>
+      <x:c r="K24" s="91"/>
+      <x:c r="L24" s="91"/>
+    </x:row>
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25" s="21"/>
       <x:c r="B25" s="21"/>
       <x:c r="C25" s="21"/>
@@ -24296,7 +24333,7 @@
       <x:c r="K25" s="21"/>
       <x:c r="L25" s="21"/>
     </x:row>
-    <x:row r="26" ht="19" customHeight="1">
+    <x:row r="26" ht="8" customHeight="1">
       <x:c r="A26" s="21"/>
       <x:c r="B26" s="21"/>
       <x:c r="C26" s="21"/>
@@ -24310,7 +24347,7 @@
       <x:c r="K26" s="21"/>
       <x:c r="L26" s="21"/>
     </x:row>
-    <x:row r="27" ht="19" customHeight="1">
+    <x:row r="27" ht="8" customHeight="1">
       <x:c r="A27" s="21"/>
       <x:c r="B27" s="21"/>
       <x:c r="C27" s="21"/>
@@ -24324,7 +24361,7 @@
       <x:c r="K27" s="21"/>
       <x:c r="L27" s="21"/>
     </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="21"/>
       <x:c r="B28" s="21"/>
       <x:c r="C28" s="21"/>
@@ -24338,7 +24375,7 @@
       <x:c r="K28" s="21"/>
       <x:c r="L28" s="21"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29" s="21"/>
       <x:c r="B29" s="21"/>
       <x:c r="C29" s="21"/>
@@ -24352,7 +24389,7 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30" s="21"/>
       <x:c r="B30" s="21"/>
       <x:c r="C30" s="21"/>
@@ -24366,7 +24403,7 @@
       <x:c r="K30" s="21"/>
       <x:c r="L30" s="21"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="21"/>
       <x:c r="C31" s="21"/>
@@ -24380,7 +24417,7 @@
       <x:c r="K31" s="21"/>
       <x:c r="L31" s="21"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="21"/>
       <x:c r="B32" s="21"/>
       <x:c r="C32" s="21"/>
@@ -24394,7 +24431,7 @@
       <x:c r="K32" s="21"/>
       <x:c r="L32" s="21"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="21"/>
       <x:c r="B33" s="21"/>
       <x:c r="C33" s="21"/>
@@ -24408,7 +24445,7 @@
       <x:c r="K33" s="21"/>
       <x:c r="L33" s="21"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34" s="21"/>
       <x:c r="B34" s="21"/>
       <x:c r="C34" s="21"/>
@@ -24422,7 +24459,7 @@
       <x:c r="K34" s="21"/>
       <x:c r="L34" s="21"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="21"/>
       <x:c r="B35" s="21"/>
       <x:c r="C35" s="21"/>
@@ -24436,7 +24473,7 @@
       <x:c r="K35" s="21"/>
       <x:c r="L35" s="21"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="21"/>
       <x:c r="B36" s="21"/>
       <x:c r="C36" s="21"/>
@@ -24450,7 +24487,7 @@
       <x:c r="K36" s="21"/>
       <x:c r="L36" s="21"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="21"/>
       <x:c r="B37" s="21"/>
       <x:c r="C37" s="21"/>
@@ -24464,7 +24501,7 @@
       <x:c r="K37" s="21"/>
       <x:c r="L37" s="21"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="21"/>
       <x:c r="C38" s="21"/>
@@ -24478,7 +24515,7 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="21"/>
       <x:c r="C39" s="21"/>
@@ -24492,7 +24529,7 @@
       <x:c r="K39" s="21"/>
       <x:c r="L39" s="21"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -24506,7 +24543,7 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -24520,7 +24557,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -24534,7 +24571,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -24548,7 +24585,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -24562,7 +24599,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -24576,7 +24613,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -24590,7 +24627,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -24604,7 +24641,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -24618,7 +24655,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -24632,7 +24669,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -24646,7 +24683,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -24660,7 +24697,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -24674,7 +24711,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -24688,7 +24725,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -24702,7 +24739,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -24716,7 +24753,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -24730,7 +24767,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -24744,7 +24781,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -24758,7 +24795,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -24772,7 +24809,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -24786,7 +24823,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -24800,7 +24837,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -24814,7 +24851,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -24828,7 +24865,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -24842,7 +24879,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -25907,9 +25944,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A23:L23"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -25932,23 +25966,23 @@
     <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="19" customHeight="1">
-      <x:c r="A1" s="30" t="str">
+    <x:row r="1" ht="27" customHeight="1">
+      <x:c r="A1" s="94" t="str">
         <x:v>Balance Sheet</x:v>
       </x:c>
-      <x:c r="B1" s="30"/>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-    </x:row>
-    <x:row r="2" ht="19" customHeight="1">
+      <x:c r="B1" s="94"/>
+      <x:c r="C1" s="95"/>
+      <x:c r="D1" s="95"/>
+      <x:c r="E1" s="95"/>
+      <x:c r="F1" s="95"/>
+      <x:c r="G1" s="95"/>
+      <x:c r="H1" s="95"/>
+      <x:c r="I1" s="95"/>
+      <x:c r="J1" s="95"/>
+      <x:c r="K1" s="95"/>
+      <x:c r="L1" s="95"/>
+    </x:row>
+    <x:row r="2" ht="8" customHeight="1">
       <x:c r="A2" s="21"/>
       <x:c r="B2" s="21"/>
       <x:c r="C2" s="21"/>
@@ -25978,7 +26012,7 @@
       <x:c r="K3" s="21"/>
       <x:c r="L3" s="21"/>
     </x:row>
-    <x:row r="4" ht="19" customHeight="1">
+    <x:row r="4" ht="8" customHeight="1">
       <x:c r="A4" s="21"/>
       <x:c r="B4" s="21"/>
       <x:c r="C4" s="21"/>
@@ -26028,7 +26062,7 @@
         <x:v>FY2031E</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="19" customHeight="1">
+    <x:row r="6" ht="8" customHeight="1">
       <x:c r="A6" s="21"/>
       <x:c r="B6" s="21"/>
       <x:c r="C6" s="21"/>
@@ -26288,7 +26322,7 @@
         <x:v>574588.3549015581</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="19" customHeight="1">
+    <x:row r="13" ht="8" customHeight="1">
       <x:c r="A13" s="21"/>
       <x:c r="B13" s="21"/>
       <x:c r="C13" s="21"/>
@@ -26302,7 +26336,7 @@
       <x:c r="K13" s="21"/>
       <x:c r="L13" s="21"/>
     </x:row>
-    <x:row r="14" ht="19" customHeight="1">
+    <x:row r="14" ht="8" customHeight="1">
       <x:c r="A14" s="21"/>
       <x:c r="B14" s="21"/>
       <x:c r="C14" s="21"/>
@@ -26700,7 +26734,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="19" customHeight="1">
+    <x:row r="24" ht="8" customHeight="1">
       <x:c r="A24" s="21"/>
       <x:c r="B24" s="21"/>
       <x:c r="C24" s="21"/>
@@ -26714,7 +26748,7 @@
       <x:c r="K24" s="21"/>
       <x:c r="L24" s="21"/>
     </x:row>
-    <x:row r="25" ht="19" customHeight="1">
+    <x:row r="25" ht="8" customHeight="1">
       <x:c r="A25" s="21"/>
       <x:c r="B25" s="21"/>
       <x:c r="C25" s="21"/>
@@ -26728,37 +26762,39 @@
       <x:c r="K25" s="21"/>
       <x:c r="L25" s="21"/>
     </x:row>
-    <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="36" t="str">
-        <x:v>Other assets and other liabilities retain FY2026 ratios to net loans. Funding debt is the explicit balancing financing requirement. Equity share capital and reserves are shown separately.</x:v>
-      </x:c>
-      <x:c r="B26" s="36"/>
-      <x:c r="C26" s="36"/>
-      <x:c r="D26" s="36"/>
-      <x:c r="E26" s="36"/>
-      <x:c r="F26" s="36"/>
-      <x:c r="G26" s="36"/>
-      <x:c r="H26" s="36"/>
-      <x:c r="I26" s="36"/>
-      <x:c r="J26" s="36"/>
-      <x:c r="K26" s="36"/>
-      <x:c r="L26" s="36"/>
+    <x:row r="26" ht="19" customHeight="1">
+      <x:c r="A26" s="91" t="str">
+        <x:v>Other assets and liabilities follow FY2026 ratios. Borrowings are the financing residual.</x:v>
+      </x:c>
+      <x:c r="B26" s="91"/>
+      <x:c r="C26" s="91"/>
+      <x:c r="D26" s="91"/>
+      <x:c r="E26" s="91"/>
+      <x:c r="F26" s="91"/>
+      <x:c r="G26" s="91"/>
+      <x:c r="H26" s="91"/>
+      <x:c r="I26" s="91"/>
+      <x:c r="J26" s="91"/>
+      <x:c r="K26" s="91"/>
+      <x:c r="L26" s="91"/>
     </x:row>
     <x:row r="27" ht="19" customHeight="1">
-      <x:c r="A27" s="21"/>
-      <x:c r="B27" s="21"/>
-      <x:c r="C27" s="21"/>
-      <x:c r="D27" s="21"/>
-      <x:c r="E27" s="21"/>
-      <x:c r="F27" s="21"/>
-      <x:c r="G27" s="21"/>
-      <x:c r="H27" s="21"/>
-      <x:c r="I27" s="21"/>
-      <x:c r="J27" s="21"/>
-      <x:c r="K27" s="21"/>
-      <x:c r="L27" s="21"/>
-    </x:row>
-    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A27" s="91" t="str">
+        <x:v>Share capital and reserves are shown separately.</x:v>
+      </x:c>
+      <x:c r="B27" s="91"/>
+      <x:c r="C27" s="91"/>
+      <x:c r="D27" s="91"/>
+      <x:c r="E27" s="91"/>
+      <x:c r="F27" s="91"/>
+      <x:c r="G27" s="91"/>
+      <x:c r="H27" s="91"/>
+      <x:c r="I27" s="91"/>
+      <x:c r="J27" s="91"/>
+      <x:c r="K27" s="91"/>
+      <x:c r="L27" s="91"/>
+    </x:row>
+    <x:row r="28" ht="8" customHeight="1">
       <x:c r="A28" s="21"/>
       <x:c r="B28" s="21"/>
       <x:c r="C28" s="21"/>
@@ -26772,7 +26808,7 @@
       <x:c r="K28" s="21"/>
       <x:c r="L28" s="21"/>
     </x:row>
-    <x:row r="29" ht="19" customHeight="1">
+    <x:row r="29" ht="8" customHeight="1">
       <x:c r="A29" s="21"/>
       <x:c r="B29" s="21"/>
       <x:c r="C29" s="21"/>
@@ -26786,7 +26822,7 @@
       <x:c r="K29" s="21"/>
       <x:c r="L29" s="21"/>
     </x:row>
-    <x:row r="30" ht="19" customHeight="1">
+    <x:row r="30" ht="8" customHeight="1">
       <x:c r="A30" s="21"/>
       <x:c r="B30" s="21"/>
       <x:c r="C30" s="21"/>
@@ -26800,7 +26836,7 @@
       <x:c r="K30" s="21"/>
       <x:c r="L30" s="21"/>
     </x:row>
-    <x:row r="31" ht="19" customHeight="1">
+    <x:row r="31" ht="8" customHeight="1">
       <x:c r="A31" s="21"/>
       <x:c r="B31" s="21"/>
       <x:c r="C31" s="21"/>
@@ -26814,7 +26850,7 @@
       <x:c r="K31" s="21"/>
       <x:c r="L31" s="21"/>
     </x:row>
-    <x:row r="32" ht="19" customHeight="1">
+    <x:row r="32" ht="8" customHeight="1">
       <x:c r="A32" s="21"/>
       <x:c r="B32" s="21"/>
       <x:c r="C32" s="21"/>
@@ -26828,7 +26864,7 @@
       <x:c r="K32" s="21"/>
       <x:c r="L32" s="21"/>
     </x:row>
-    <x:row r="33" ht="19" customHeight="1">
+    <x:row r="33" ht="8" customHeight="1">
       <x:c r="A33" s="21"/>
       <x:c r="B33" s="21"/>
       <x:c r="C33" s="21"/>
@@ -26842,7 +26878,7 @@
       <x:c r="K33" s="21"/>
       <x:c r="L33" s="21"/>
     </x:row>
-    <x:row r="34" ht="19" customHeight="1">
+    <x:row r="34" ht="8" customHeight="1">
       <x:c r="A34" s="21"/>
       <x:c r="B34" s="21"/>
       <x:c r="C34" s="21"/>
@@ -26856,7 +26892,7 @@
       <x:c r="K34" s="21"/>
       <x:c r="L34" s="21"/>
     </x:row>
-    <x:row r="35" ht="19" customHeight="1">
+    <x:row r="35" ht="8" customHeight="1">
       <x:c r="A35" s="21"/>
       <x:c r="B35" s="21"/>
       <x:c r="C35" s="21"/>
@@ -26870,7 +26906,7 @@
       <x:c r="K35" s="21"/>
       <x:c r="L35" s="21"/>
     </x:row>
-    <x:row r="36" ht="19" customHeight="1">
+    <x:row r="36" ht="8" customHeight="1">
       <x:c r="A36" s="21"/>
       <x:c r="B36" s="21"/>
       <x:c r="C36" s="21"/>
@@ -26884,7 +26920,7 @@
       <x:c r="K36" s="21"/>
       <x:c r="L36" s="21"/>
     </x:row>
-    <x:row r="37" ht="19" customHeight="1">
+    <x:row r="37" ht="8" customHeight="1">
       <x:c r="A37" s="21"/>
       <x:c r="B37" s="21"/>
       <x:c r="C37" s="21"/>
@@ -26898,7 +26934,7 @@
       <x:c r="K37" s="21"/>
       <x:c r="L37" s="21"/>
     </x:row>
-    <x:row r="38" ht="19" customHeight="1">
+    <x:row r="38" ht="8" customHeight="1">
       <x:c r="A38" s="21"/>
       <x:c r="B38" s="21"/>
       <x:c r="C38" s="21"/>
@@ -26912,7 +26948,7 @@
       <x:c r="K38" s="21"/>
       <x:c r="L38" s="21"/>
     </x:row>
-    <x:row r="39" ht="19" customHeight="1">
+    <x:row r="39" ht="8" customHeight="1">
       <x:c r="A39" s="21"/>
       <x:c r="B39" s="21"/>
       <x:c r="C39" s="21"/>
@@ -26926,7 +26962,7 @@
       <x:c r="K39" s="21"/>
       <x:c r="L39" s="21"/>
     </x:row>
-    <x:row r="40" ht="19" customHeight="1">
+    <x:row r="40" ht="8" customHeight="1">
       <x:c r="A40" s="21"/>
       <x:c r="B40" s="21"/>
       <x:c r="C40" s="21"/>
@@ -26940,7 +26976,7 @@
       <x:c r="K40" s="21"/>
       <x:c r="L40" s="21"/>
     </x:row>
-    <x:row r="41" ht="19" customHeight="1">
+    <x:row r="41" ht="8" customHeight="1">
       <x:c r="A41" s="21"/>
       <x:c r="B41" s="21"/>
       <x:c r="C41" s="21"/>
@@ -26954,7 +26990,7 @@
       <x:c r="K41" s="21"/>
       <x:c r="L41" s="21"/>
     </x:row>
-    <x:row r="42" ht="19" customHeight="1">
+    <x:row r="42" ht="8" customHeight="1">
       <x:c r="A42" s="21"/>
       <x:c r="B42" s="21"/>
       <x:c r="C42" s="21"/>
@@ -26968,7 +27004,7 @@
       <x:c r="K42" s="21"/>
       <x:c r="L42" s="21"/>
     </x:row>
-    <x:row r="43" ht="19" customHeight="1">
+    <x:row r="43" ht="8" customHeight="1">
       <x:c r="A43" s="21"/>
       <x:c r="B43" s="21"/>
       <x:c r="C43" s="21"/>
@@ -26982,7 +27018,7 @@
       <x:c r="K43" s="21"/>
       <x:c r="L43" s="21"/>
     </x:row>
-    <x:row r="44" ht="19" customHeight="1">
+    <x:row r="44" ht="8" customHeight="1">
       <x:c r="A44" s="21"/>
       <x:c r="B44" s="21"/>
       <x:c r="C44" s="21"/>
@@ -26996,7 +27032,7 @@
       <x:c r="K44" s="21"/>
       <x:c r="L44" s="21"/>
     </x:row>
-    <x:row r="45" ht="19" customHeight="1">
+    <x:row r="45" ht="8" customHeight="1">
       <x:c r="A45" s="21"/>
       <x:c r="B45" s="21"/>
       <x:c r="C45" s="21"/>
@@ -27010,7 +27046,7 @@
       <x:c r="K45" s="21"/>
       <x:c r="L45" s="21"/>
     </x:row>
-    <x:row r="46" ht="19" customHeight="1">
+    <x:row r="46" ht="8" customHeight="1">
       <x:c r="A46" s="21"/>
       <x:c r="B46" s="21"/>
       <x:c r="C46" s="21"/>
@@ -27024,7 +27060,7 @@
       <x:c r="K46" s="21"/>
       <x:c r="L46" s="21"/>
     </x:row>
-    <x:row r="47" ht="19" customHeight="1">
+    <x:row r="47" ht="8" customHeight="1">
       <x:c r="A47" s="21"/>
       <x:c r="B47" s="21"/>
       <x:c r="C47" s="21"/>
@@ -27038,7 +27074,7 @@
       <x:c r="K47" s="21"/>
       <x:c r="L47" s="21"/>
     </x:row>
-    <x:row r="48" ht="19" customHeight="1">
+    <x:row r="48" ht="8" customHeight="1">
       <x:c r="A48" s="21"/>
       <x:c r="B48" s="21"/>
       <x:c r="C48" s="21"/>
@@ -27052,7 +27088,7 @@
       <x:c r="K48" s="21"/>
       <x:c r="L48" s="21"/>
     </x:row>
-    <x:row r="49" ht="19" customHeight="1">
+    <x:row r="49" ht="8" customHeight="1">
       <x:c r="A49" s="21"/>
       <x:c r="B49" s="21"/>
       <x:c r="C49" s="21"/>
@@ -27066,7 +27102,7 @@
       <x:c r="K49" s="21"/>
       <x:c r="L49" s="21"/>
     </x:row>
-    <x:row r="50" ht="19" customHeight="1">
+    <x:row r="50" ht="8" customHeight="1">
       <x:c r="A50" s="21"/>
       <x:c r="B50" s="21"/>
       <x:c r="C50" s="21"/>
@@ -27080,7 +27116,7 @@
       <x:c r="K50" s="21"/>
       <x:c r="L50" s="21"/>
     </x:row>
-    <x:row r="51" ht="19" customHeight="1">
+    <x:row r="51" ht="8" customHeight="1">
       <x:c r="A51" s="21"/>
       <x:c r="B51" s="21"/>
       <x:c r="C51" s="21"/>
@@ -27094,7 +27130,7 @@
       <x:c r="K51" s="21"/>
       <x:c r="L51" s="21"/>
     </x:row>
-    <x:row r="52" ht="19" customHeight="1">
+    <x:row r="52" ht="8" customHeight="1">
       <x:c r="A52" s="21"/>
       <x:c r="B52" s="21"/>
       <x:c r="C52" s="21"/>
@@ -27108,7 +27144,7 @@
       <x:c r="K52" s="21"/>
       <x:c r="L52" s="21"/>
     </x:row>
-    <x:row r="53" ht="19" customHeight="1">
+    <x:row r="53" ht="8" customHeight="1">
       <x:c r="A53" s="21"/>
       <x:c r="B53" s="21"/>
       <x:c r="C53" s="21"/>
@@ -27122,7 +27158,7 @@
       <x:c r="K53" s="21"/>
       <x:c r="L53" s="21"/>
     </x:row>
-    <x:row r="54" ht="19" customHeight="1">
+    <x:row r="54" ht="8" customHeight="1">
       <x:c r="A54" s="21"/>
       <x:c r="B54" s="21"/>
       <x:c r="C54" s="21"/>
@@ -27136,7 +27172,7 @@
       <x:c r="K54" s="21"/>
       <x:c r="L54" s="21"/>
     </x:row>
-    <x:row r="55" ht="19" customHeight="1">
+    <x:row r="55" ht="8" customHeight="1">
       <x:c r="A55" s="21"/>
       <x:c r="B55" s="21"/>
       <x:c r="C55" s="21"/>
@@ -27150,7 +27186,7 @@
       <x:c r="K55" s="21"/>
       <x:c r="L55" s="21"/>
     </x:row>
-    <x:row r="56" ht="19" customHeight="1">
+    <x:row r="56" ht="8" customHeight="1">
       <x:c r="A56" s="21"/>
       <x:c r="B56" s="21"/>
       <x:c r="C56" s="21"/>
@@ -27164,7 +27200,7 @@
       <x:c r="K56" s="21"/>
       <x:c r="L56" s="21"/>
     </x:row>
-    <x:row r="57" ht="19" customHeight="1">
+    <x:row r="57" ht="8" customHeight="1">
       <x:c r="A57" s="21"/>
       <x:c r="B57" s="21"/>
       <x:c r="C57" s="21"/>
@@ -27178,7 +27214,7 @@
       <x:c r="K57" s="21"/>
       <x:c r="L57" s="21"/>
     </x:row>
-    <x:row r="58" ht="19" customHeight="1">
+    <x:row r="58" ht="8" customHeight="1">
       <x:c r="A58" s="21"/>
       <x:c r="B58" s="21"/>
       <x:c r="C58" s="21"/>
@@ -27192,7 +27228,7 @@
       <x:c r="K58" s="21"/>
       <x:c r="L58" s="21"/>
     </x:row>
-    <x:row r="59" ht="19" customHeight="1">
+    <x:row r="59" ht="8" customHeight="1">
       <x:c r="A59" s="21"/>
       <x:c r="B59" s="21"/>
       <x:c r="C59" s="21"/>
@@ -27206,7 +27242,7 @@
       <x:c r="K59" s="21"/>
       <x:c r="L59" s="21"/>
     </x:row>
-    <x:row r="60" ht="19" customHeight="1">
+    <x:row r="60" ht="8" customHeight="1">
       <x:c r="A60" s="21"/>
       <x:c r="B60" s="21"/>
       <x:c r="C60" s="21"/>
@@ -27220,7 +27256,7 @@
       <x:c r="K60" s="21"/>
       <x:c r="L60" s="21"/>
     </x:row>
-    <x:row r="61" ht="19" customHeight="1">
+    <x:row r="61" ht="8" customHeight="1">
       <x:c r="A61" s="21"/>
       <x:c r="B61" s="21"/>
       <x:c r="C61" s="21"/>
@@ -27234,7 +27270,7 @@
       <x:c r="K61" s="21"/>
       <x:c r="L61" s="21"/>
     </x:row>
-    <x:row r="62" ht="19" customHeight="1">
+    <x:row r="62" ht="8" customHeight="1">
       <x:c r="A62" s="21"/>
       <x:c r="B62" s="21"/>
       <x:c r="C62" s="21"/>
@@ -27248,7 +27284,7 @@
       <x:c r="K62" s="21"/>
       <x:c r="L62" s="21"/>
     </x:row>
-    <x:row r="63" ht="19" customHeight="1">
+    <x:row r="63" ht="8" customHeight="1">
       <x:c r="A63" s="21"/>
       <x:c r="B63" s="21"/>
       <x:c r="C63" s="21"/>
@@ -27262,7 +27298,7 @@
       <x:c r="K63" s="21"/>
       <x:c r="L63" s="21"/>
     </x:row>
-    <x:row r="64" ht="19" customHeight="1">
+    <x:row r="64" ht="8" customHeight="1">
       <x:c r="A64" s="21"/>
       <x:c r="B64" s="21"/>
       <x:c r="C64" s="21"/>
@@ -27276,7 +27312,7 @@
       <x:c r="K64" s="21"/>
       <x:c r="L64" s="21"/>
     </x:row>
-    <x:row r="65" ht="19" customHeight="1">
+    <x:row r="65" ht="8" customHeight="1">
       <x:c r="A65" s="21"/>
       <x:c r="B65" s="21"/>
       <x:c r="C65" s="21"/>
@@ -28341,9 +28377,6 @@
       <x:c r="L140" s="21"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A26:L26"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>